--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA12A3EF-ECA8-BF42-8CF6-C324C0AD30A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDCD6CC-7EFF-4A4D-9FCA-A015240CCB72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="215">
   <si>
     <t>日期</t>
   </si>
@@ -475,13 +475,244 @@
   <si>
     <t>1-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隊伍 A</t>
+  </si>
+  <si>
+    <t>隊伍 B</t>
+  </si>
+  <si>
+    <t>比分</t>
+  </si>
+  <si>
+    <t>14/4 二</t>
+  </si>
+  <si>
+    <t>鎚鐵 - 中華</t>
+  </si>
+  <si>
+    <t>鎚鐵 - 全能</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>水電 - 毅成</t>
+  </si>
+  <si>
+    <t>屠宰 - 狂熱者</t>
+  </si>
+  <si>
+    <t>公務 - 富利來</t>
+  </si>
+  <si>
+    <t>公務 - 紅纖</t>
+  </si>
+  <si>
+    <t>的士 - 利士</t>
+  </si>
+  <si>
+    <t>鎚鐵 - 興發</t>
+  </si>
+  <si>
+    <t>造船 - 新橋仔</t>
+  </si>
+  <si>
+    <t>水電 - 花園 B</t>
+  </si>
+  <si>
+    <t>水電 - 花園 A</t>
+  </si>
+  <si>
+    <t>16/4 四</t>
+  </si>
+  <si>
+    <t>鎚鐵 - 自由人</t>
+  </si>
+  <si>
+    <t>的士 - 旺記</t>
+  </si>
+  <si>
+    <t>屠宰 - 紅魔鬼</t>
+  </si>
+  <si>
+    <t>21/4 二</t>
+  </si>
+  <si>
+    <t>23/4 四</t>
+  </si>
+  <si>
+    <t>28/4 二</t>
+  </si>
+  <si>
+    <t>30/4 四</t>
+  </si>
+  <si>
+    <t>元 A</t>
+  </si>
+  <si>
+    <t>元 B</t>
+  </si>
+  <si>
+    <t>元 C</t>
+  </si>
+  <si>
+    <t>造船 - 新橋仔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15/4 三</t>
+  </si>
+  <si>
+    <t>製造 - 台星</t>
+  </si>
+  <si>
+    <t>工武 - 新興</t>
+  </si>
+  <si>
+    <t>高 A1</t>
+  </si>
+  <si>
+    <t>海員 - 宇宙猩</t>
+  </si>
+  <si>
+    <t>高 B1</t>
+  </si>
+  <si>
+    <t>康樂 - 新花城</t>
+  </si>
+  <si>
+    <t>北綜 - 士砵亭</t>
+  </si>
+  <si>
+    <t>康樂 - 新金華</t>
+  </si>
+  <si>
+    <t>康樂 - 閃蜂</t>
+  </si>
+  <si>
+    <t>服總 - 恆勢</t>
+  </si>
+  <si>
+    <t>屠宰 - 棘刺</t>
+  </si>
+  <si>
+    <t>工武 - 聯樂</t>
+  </si>
+  <si>
+    <t>22/4 三</t>
+  </si>
+  <si>
+    <t>高 B2</t>
+  </si>
+  <si>
+    <t>製造 - 灝庭</t>
+  </si>
+  <si>
+    <t>高 A2</t>
+  </si>
+  <si>
+    <t>29/4 三</t>
+  </si>
+  <si>
+    <t>高 A3</t>
+  </si>
+  <si>
+    <t>高 B3</t>
+  </si>
+  <si>
+    <t>北綜 - 路協</t>
+  </si>
+  <si>
+    <t>中 A1</t>
+  </si>
+  <si>
+    <t>公務 - 寧安</t>
+  </si>
+  <si>
+    <t>康友 - 金星</t>
+  </si>
+  <si>
+    <t>公車 - 迎風</t>
+  </si>
+  <si>
+    <t>屠宰 - 嘉華</t>
+  </si>
+  <si>
+    <t>17/4 五</t>
+  </si>
+  <si>
+    <t>休閒 - 二合一</t>
+  </si>
+  <si>
+    <t>商僱 - 嘉賢聯</t>
+  </si>
+  <si>
+    <t>中 B1</t>
+  </si>
+  <si>
+    <t>中 C1</t>
+  </si>
+  <si>
+    <t>公務 - 夜星會</t>
+  </si>
+  <si>
+    <t>公務 - 聯合</t>
+  </si>
+  <si>
+    <t>休閒 - 澳義</t>
+  </si>
+  <si>
+    <t>疋服 - 業餘</t>
+  </si>
+  <si>
+    <t>麵飽 - PAPA</t>
+  </si>
+  <si>
+    <t>中 C2</t>
+  </si>
+  <si>
+    <t>24/4 五</t>
+  </si>
+  <si>
+    <t>中 B2</t>
+  </si>
+  <si>
+    <t>中 A2</t>
+  </si>
+  <si>
+    <t>中 A3</t>
+  </si>
+  <si>
+    <t>20/4 一</t>
+  </si>
+  <si>
+    <t>豬膽 - 六六 A</t>
+  </si>
+  <si>
+    <t>27/4 一</t>
+  </si>
+  <si>
+    <t>初 A4</t>
+  </si>
+  <si>
+    <t>4/5 一</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -499,6 +730,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="新細明體"/>
@@ -529,7 +768,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -543,6 +782,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -859,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E0EA83-C783-7140-AD8B-B43A843048C1}">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
@@ -1747,7 +1992,7 @@
         <v>95</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1770,7 +2015,7 @@
         <v>98</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1793,7 +2038,7 @@
         <v>82</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1816,7 +2061,7 @@
         <v>98</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1839,7 +2084,7 @@
         <v>98</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1862,7 +2107,7 @@
         <v>82</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3105,6 +3350,489 @@
       </c>
       <c r="G97" s="4" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C98" t="s">
+        <v>58</v>
+      </c>
+      <c r="D98" t="s">
+        <v>55</v>
+      </c>
+      <c r="E98" t="s">
+        <v>80</v>
+      </c>
+      <c r="F98" t="s">
+        <v>91</v>
+      </c>
+      <c r="G98" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C99" t="s">
+        <v>62</v>
+      </c>
+      <c r="D99" t="s">
+        <v>59</v>
+      </c>
+      <c r="E99" t="s">
+        <v>79</v>
+      </c>
+      <c r="F99" t="s">
+        <v>92</v>
+      </c>
+      <c r="G99" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>210</v>
+      </c>
+      <c r="B100" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C100" t="s">
+        <v>63</v>
+      </c>
+      <c r="D100" t="s">
+        <v>60</v>
+      </c>
+      <c r="E100" t="s">
+        <v>80</v>
+      </c>
+      <c r="F100" t="s">
+        <v>92</v>
+      </c>
+      <c r="G100" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C101" t="s">
+        <v>67</v>
+      </c>
+      <c r="D101" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" t="s">
+        <v>79</v>
+      </c>
+      <c r="F101" t="s">
+        <v>93</v>
+      </c>
+      <c r="G101" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>210</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" t="s">
+        <v>80</v>
+      </c>
+      <c r="F102" t="s">
+        <v>93</v>
+      </c>
+      <c r="G102" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>210</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C103" t="s">
+        <v>72</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" t="s">
+        <v>79</v>
+      </c>
+      <c r="F103" t="s">
+        <v>94</v>
+      </c>
+      <c r="G103" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>210</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C104" t="s">
+        <v>211</v>
+      </c>
+      <c r="D104" t="s">
+        <v>70</v>
+      </c>
+      <c r="E104" t="s">
+        <v>80</v>
+      </c>
+      <c r="F104" t="s">
+        <v>94</v>
+      </c>
+      <c r="G104" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>162</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C105" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" t="s">
+        <v>74</v>
+      </c>
+      <c r="E105" t="s">
+        <v>80</v>
+      </c>
+      <c r="F105" t="s">
+        <v>95</v>
+      </c>
+      <c r="G105" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C106" t="s">
+        <v>78</v>
+      </c>
+      <c r="D106" t="s">
+        <v>75</v>
+      </c>
+      <c r="E106" t="s">
+        <v>79</v>
+      </c>
+      <c r="F106" t="s">
+        <v>95</v>
+      </c>
+      <c r="G106" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
+        <v>80</v>
+      </c>
+      <c r="F107" t="s">
+        <v>213</v>
+      </c>
+      <c r="G107" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C108" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
+        <v>79</v>
+      </c>
+      <c r="F108" t="s">
+        <v>213</v>
+      </c>
+      <c r="G108" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>212</v>
+      </c>
+      <c r="B109" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C109" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" t="s">
+        <v>4</v>
+      </c>
+      <c r="E109" t="s">
+        <v>80</v>
+      </c>
+      <c r="F109" t="s">
+        <v>213</v>
+      </c>
+      <c r="G109" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>212</v>
+      </c>
+      <c r="B110" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s">
+        <v>79</v>
+      </c>
+      <c r="F110" t="s">
+        <v>82</v>
+      </c>
+      <c r="G110" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>212</v>
+      </c>
+      <c r="B111" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" t="s">
+        <v>80</v>
+      </c>
+      <c r="F111" t="s">
+        <v>82</v>
+      </c>
+      <c r="G111" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="s">
+        <v>80</v>
+      </c>
+      <c r="F112" t="s">
+        <v>83</v>
+      </c>
+      <c r="G112" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>214</v>
+      </c>
+      <c r="B113" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C113" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>79</v>
+      </c>
+      <c r="F113" t="s">
+        <v>83</v>
+      </c>
+      <c r="G113" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C114" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" t="s">
+        <v>80</v>
+      </c>
+      <c r="F114" t="s">
+        <v>84</v>
+      </c>
+      <c r="G114" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>214</v>
+      </c>
+      <c r="B115" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C115" t="s">
+        <v>20</v>
+      </c>
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" t="s">
+        <v>79</v>
+      </c>
+      <c r="F115" t="s">
+        <v>84</v>
+      </c>
+      <c r="G115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>214</v>
+      </c>
+      <c r="B116" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C116" t="s">
+        <v>28</v>
+      </c>
+      <c r="D116" t="s">
+        <v>29</v>
+      </c>
+      <c r="E116" t="s">
+        <v>80</v>
+      </c>
+      <c r="F116" t="s">
+        <v>85</v>
+      </c>
+      <c r="G116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>214</v>
+      </c>
+      <c r="B117" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C117" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E117" t="s">
+        <v>79</v>
+      </c>
+      <c r="F117" t="s">
+        <v>85</v>
+      </c>
+      <c r="G117" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>214</v>
+      </c>
+      <c r="B118" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C118" t="s">
+        <v>33</v>
+      </c>
+      <c r="D118" t="s">
+        <v>34</v>
+      </c>
+      <c r="E118" t="s">
+        <v>80</v>
+      </c>
+      <c r="F118" t="s">
+        <v>86</v>
+      </c>
+      <c r="G118" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3116,9 +3844,455 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A652382C-1B8E-3D47-8B07-5935E173CD82}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>188</v>
+      </c>
+      <c r="G19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3126,9 +4300,523 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B38FBF-5FEC-5740-9062-B8355DB1F4DA}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C18" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3136,9 +4824,591 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F9B54F-1C5B-D04D-993A-929D11ED7A52}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" t="s">
+        <v>167</v>
+      </c>
+      <c r="G16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="6">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDCD6CC-7EFF-4A4D-9FCA-A015240CCB72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6232A3ED-E9FA-CF46-9577-0412E03B3352}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="207">
   <si>
     <t>日期</t>
   </si>
@@ -579,15 +579,9 @@
     <t>工武 - 新興</t>
   </si>
   <si>
-    <t>高 A1</t>
-  </si>
-  <si>
     <t>海員 - 宇宙猩</t>
   </si>
   <si>
-    <t>高 B1</t>
-  </si>
-  <si>
     <t>康樂 - 新花城</t>
   </si>
   <si>
@@ -612,30 +606,15 @@
     <t>22/4 三</t>
   </si>
   <si>
-    <t>高 B2</t>
-  </si>
-  <si>
     <t>製造 - 灝庭</t>
   </si>
   <si>
-    <t>高 A2</t>
-  </si>
-  <si>
     <t>29/4 三</t>
   </si>
   <si>
-    <t>高 A3</t>
-  </si>
-  <si>
-    <t>高 B3</t>
-  </si>
-  <si>
     <t>北綜 - 路協</t>
   </si>
   <si>
-    <t>中 A1</t>
-  </si>
-  <si>
     <t>公務 - 寧安</t>
   </si>
   <si>
@@ -657,12 +636,6 @@
     <t>商僱 - 嘉賢聯</t>
   </si>
   <si>
-    <t>中 B1</t>
-  </si>
-  <si>
-    <t>中 C1</t>
-  </si>
-  <si>
     <t>公務 - 夜星會</t>
   </si>
   <si>
@@ -678,21 +651,9 @@
     <t>麵飽 - PAPA</t>
   </si>
   <si>
-    <t>中 C2</t>
-  </si>
-  <si>
     <t>24/4 五</t>
   </si>
   <si>
-    <t>中 B2</t>
-  </si>
-  <si>
-    <t>中 A2</t>
-  </si>
-  <si>
-    <t>中 A3</t>
-  </si>
-  <si>
     <t>20/4 一</t>
   </si>
   <si>
@@ -702,10 +663,26 @@
     <t>27/4 一</t>
   </si>
   <si>
-    <t>初 A4</t>
-  </si>
-  <si>
     <t>4/5 一</t>
+  </si>
+  <si>
+    <t>高 A</t>
+  </si>
+  <si>
+    <t>高 A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高 B</t>
+  </si>
+  <si>
+    <t>中 A</t>
+  </si>
+  <si>
+    <t>中 B</t>
+  </si>
+  <si>
+    <t>中 C</t>
   </si>
 </sst>
 </file>
@@ -3377,7 +3354,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B99" s="2">
         <v>0.8125</v>
@@ -3400,7 +3377,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B100" s="2">
         <v>0.8125</v>
@@ -3423,7 +3400,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B101" s="2">
         <v>0.85416666666666663</v>
@@ -3446,7 +3423,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B102" s="2">
         <v>0.85416666666666663</v>
@@ -3469,7 +3446,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B103" s="2">
         <v>0.89583333333333337</v>
@@ -3492,13 +3469,13 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B104" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="D104" t="s">
         <v>70</v>
@@ -3538,7 +3515,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B106" s="2">
         <v>0.8125</v>
@@ -3561,7 +3538,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B107" s="2">
         <v>0.8125</v>
@@ -3576,7 +3553,7 @@
         <v>80</v>
       </c>
       <c r="F107" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="G107" t="s">
         <v>147</v>
@@ -3584,7 +3561,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B108" s="2">
         <v>0.85416666666666663</v>
@@ -3599,7 +3576,7 @@
         <v>79</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="G108" t="s">
         <v>147</v>
@@ -3607,7 +3584,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B109" s="2">
         <v>0.85416666666666663</v>
@@ -3622,7 +3599,7 @@
         <v>80</v>
       </c>
       <c r="F109" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="G109" t="s">
         <v>147</v>
@@ -3630,7 +3607,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B110" s="2">
         <v>0.89583333333333337</v>
@@ -3653,7 +3630,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B111" s="2">
         <v>0.89583333333333337</v>
@@ -3699,7 +3676,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B113" s="2">
         <v>0.8125</v>
@@ -3722,7 +3699,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B114" s="2">
         <v>0.8125</v>
@@ -3745,7 +3722,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B115" s="2">
         <v>0.85416666666666663</v>
@@ -3768,7 +3745,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B116" s="2">
         <v>0.85416666666666663</v>
@@ -3791,7 +3768,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B117" s="2">
         <v>0.89583333333333337</v>
@@ -3814,7 +3791,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B118" s="2">
         <v>0.89583333333333337</v>
@@ -3895,7 +3872,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="G2" t="s">
         <v>147</v>
@@ -3912,13 +3889,13 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G3" t="s">
         <v>147</v>
@@ -3932,16 +3909,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
         <v>147</v>
@@ -3955,7 +3932,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -3964,7 +3941,7 @@
         <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G5" t="s">
         <v>147</v>
@@ -3978,16 +3955,16 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
         <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G6" t="s">
         <v>147</v>
@@ -4001,16 +3978,16 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G7" t="s">
         <v>147</v>
@@ -4018,22 +3995,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B8" s="2">
         <v>0.8125</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G8" t="s">
         <v>147</v>
@@ -4041,13 +4018,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B9" s="2">
         <v>0.8125</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
         <v>170</v>
@@ -4056,7 +4033,7 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="G9" t="s">
         <v>147</v>
@@ -4064,7 +4041,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" s="2">
         <v>0.85416666666666663</v>
@@ -4079,7 +4056,7 @@
         <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G10" t="s">
         <v>147</v>
@@ -4087,7 +4064,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" s="2">
         <v>0.85416666666666663</v>
@@ -4096,13 +4073,13 @@
         <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="G11" t="s">
         <v>147</v>
@@ -4110,22 +4087,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B12" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G12" t="s">
         <v>147</v>
@@ -4133,22 +4110,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" t="s">
         <v>176</v>
       </c>
-      <c r="D13" t="s">
-        <v>178</v>
-      </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="G13" t="s">
         <v>147</v>
@@ -4156,22 +4133,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
         <v>147</v>
@@ -4179,7 +4156,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
@@ -4188,13 +4165,13 @@
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G15" t="s">
         <v>147</v>
@@ -4202,7 +4179,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
@@ -4211,13 +4188,13 @@
         <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
         <v>147</v>
@@ -4225,22 +4202,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G17" t="s">
         <v>147</v>
@@ -4248,22 +4225,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
         <v>147</v>
@@ -4271,7 +4248,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
@@ -4280,13 +4257,13 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G19" t="s">
         <v>147</v>
@@ -4341,7 +4318,7 @@
         <v>0.8125</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
         <v>170</v>
@@ -4350,7 +4327,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="G2" t="s">
         <v>147</v>
@@ -4364,16 +4341,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
         <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="G3" t="s">
         <v>147</v>
@@ -4387,16 +4364,16 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="G4" t="s">
         <v>147</v>
@@ -4404,22 +4381,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2">
         <v>0.8125</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G5" t="s">
         <v>147</v>
@@ -4427,7 +4404,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2">
         <v>0.8125</v>
@@ -4442,7 +4419,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G6" t="s">
         <v>147</v>
@@ -4450,22 +4427,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B7" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G7" t="s">
         <v>147</v>
@@ -4473,22 +4450,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B8" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G8" t="s">
         <v>147</v>
@@ -4496,7 +4473,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2">
         <v>0.89583333333333337</v>
@@ -4505,13 +4482,13 @@
         <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G9" t="s">
         <v>147</v>
@@ -4519,7 +4496,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B10" s="2">
         <v>0.89583333333333337</v>
@@ -4528,13 +4505,13 @@
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G10" t="s">
         <v>147</v>
@@ -4548,7 +4525,7 @@
         <v>0.8125</v>
       </c>
       <c r="C11" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
         <v>160</v>
@@ -4557,7 +4534,7 @@
         <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G11" t="s">
         <v>147</v>
@@ -4574,13 +4551,13 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G12" t="s">
         <v>147</v>
@@ -4594,7 +4571,7 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
         <v>55</v>
@@ -4603,7 +4580,7 @@
         <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G13" t="s">
         <v>147</v>
@@ -4611,13 +4588,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -4626,7 +4603,7 @@
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G14" t="s">
         <v>147</v>
@@ -4634,22 +4611,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G15" t="s">
         <v>147</v>
@@ -4657,22 +4634,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G16" t="s">
         <v>147</v>
@@ -4680,22 +4657,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G17" t="s">
         <v>147</v>
@@ -4703,22 +4680,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G18" t="s">
         <v>147</v>
@@ -4726,13 +4703,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
         <v>170</v>
@@ -4741,7 +4718,7 @@
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G19" t="s">
         <v>147</v>
@@ -4755,16 +4732,16 @@
         <v>0.8125</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G20" t="s">
         <v>147</v>
@@ -4781,13 +4758,13 @@
         <v>170</v>
       </c>
       <c r="D21" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G21" t="s">
         <v>147</v>
@@ -4801,16 +4778,16 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G22" t="s">
         <v>147</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6232A3ED-E9FA-CF46-9577-0412E03B3352}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDDD7F3-FC82-1A41-A44A-384EBCACB8A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="205">
   <si>
     <t>日期</t>
   </si>
@@ -483,12 +483,6 @@
   <si>
     <t>4-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>隊伍 A</t>
-  </si>
-  <si>
-    <t>隊伍 B</t>
   </si>
   <si>
     <t>比分</t>
@@ -3331,7 +3325,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B98" s="2">
         <v>0.89583333333333337</v>
@@ -3349,12 +3343,12 @@
         <v>91</v>
       </c>
       <c r="G98" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B99" s="2">
         <v>0.8125</v>
@@ -3372,12 +3366,12 @@
         <v>92</v>
       </c>
       <c r="G99" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B100" s="2">
         <v>0.8125</v>
@@ -3395,12 +3389,12 @@
         <v>92</v>
       </c>
       <c r="G100" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B101" s="2">
         <v>0.85416666666666663</v>
@@ -3418,12 +3412,12 @@
         <v>93</v>
       </c>
       <c r="G101" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B102" s="2">
         <v>0.85416666666666663</v>
@@ -3441,12 +3435,12 @@
         <v>93</v>
       </c>
       <c r="G102" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B103" s="2">
         <v>0.89583333333333337</v>
@@ -3464,18 +3458,18 @@
         <v>94</v>
       </c>
       <c r="G103" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B104" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C104" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D104" t="s">
         <v>70</v>
@@ -3487,12 +3481,12 @@
         <v>94</v>
       </c>
       <c r="G104" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B105" s="2">
         <v>0.89583333333333337</v>
@@ -3510,12 +3504,12 @@
         <v>95</v>
       </c>
       <c r="G105" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B106" s="2">
         <v>0.8125</v>
@@ -3533,12 +3527,12 @@
         <v>95</v>
       </c>
       <c r="G106" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B107" s="2">
         <v>0.8125</v>
@@ -3556,12 +3550,12 @@
         <v>98</v>
       </c>
       <c r="G107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B108" s="2">
         <v>0.85416666666666663</v>
@@ -3579,12 +3573,12 @@
         <v>98</v>
       </c>
       <c r="G108" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B109" s="2">
         <v>0.85416666666666663</v>
@@ -3602,12 +3596,12 @@
         <v>98</v>
       </c>
       <c r="G109" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B110" s="2">
         <v>0.89583333333333337</v>
@@ -3625,12 +3619,12 @@
         <v>82</v>
       </c>
       <c r="G110" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B111" s="2">
         <v>0.89583333333333337</v>
@@ -3648,12 +3642,12 @@
         <v>82</v>
       </c>
       <c r="G111" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B112" s="2">
         <v>0.89583333333333337</v>
@@ -3671,12 +3665,12 @@
         <v>83</v>
       </c>
       <c r="G112" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B113" s="2">
         <v>0.8125</v>
@@ -3694,12 +3688,12 @@
         <v>83</v>
       </c>
       <c r="G113" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B114" s="2">
         <v>0.8125</v>
@@ -3717,12 +3711,12 @@
         <v>84</v>
       </c>
       <c r="G114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B115" s="2">
         <v>0.85416666666666663</v>
@@ -3740,12 +3734,12 @@
         <v>84</v>
       </c>
       <c r="G115" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B116" s="2">
         <v>0.85416666666666663</v>
@@ -3763,12 +3757,12 @@
         <v>85</v>
       </c>
       <c r="G116" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B117" s="2">
         <v>0.89583333333333337</v>
@@ -3786,12 +3780,12 @@
         <v>85</v>
       </c>
       <c r="G117" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B118" s="2">
         <v>0.89583333333333337</v>
@@ -3809,7 +3803,7 @@
         <v>86</v>
       </c>
       <c r="G118" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3840,10 +3834,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -3852,35 +3846,35 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D2" t="s">
-        <v>171</v>
-      </c>
       <c r="E2" t="s">
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B3" s="2">
         <v>0.8125</v>
@@ -3889,50 +3883,50 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
         <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B4" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -3941,107 +3935,107 @@
         <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B6" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B8" s="2">
         <v>0.8125</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E8" t="s">
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B9" s="2">
         <v>0.8125</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E9" t="s">
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B10" s="2">
         <v>0.85416666666666663</v>
@@ -4056,107 +4050,107 @@
         <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B11" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B12" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
         <v>174</v>
       </c>
-      <c r="D13" t="s">
-        <v>176</v>
-      </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
@@ -4165,90 +4159,90 @@
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
@@ -4257,16 +4251,16 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4295,10 +4289,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -4307,104 +4301,104 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B2" s="2">
         <v>0.8125</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B3" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
         <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D5" t="s">
-        <v>190</v>
-      </c>
       <c r="E5" t="s">
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B6" s="2">
         <v>0.8125</v>
@@ -4419,61 +4413,61 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B7" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E7" t="s">
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B8" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B9" s="2">
         <v>0.89583333333333337</v>
@@ -4482,67 +4476,67 @@
         <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B11" s="2">
         <v>0.8125</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
         <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
@@ -4551,27 +4545,27 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D13" t="s">
         <v>55</v>
@@ -4580,21 +4574,21 @@
         <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -4603,194 +4597,194 @@
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
       </c>
       <c r="C15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
         <v>184</v>
       </c>
-      <c r="D15" t="s">
-        <v>186</v>
-      </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" t="s">
         <v>183</v>
       </c>
-      <c r="D17" t="s">
-        <v>185</v>
-      </c>
       <c r="E17" t="s">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B20" s="2">
         <v>0.8125</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
         <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B22" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" t="s">
         <v>185</v>
       </c>
-      <c r="D22" t="s">
-        <v>187</v>
-      </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4818,10 +4812,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -4830,41 +4824,41 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" t="s">
-        <v>146</v>
-      </c>
       <c r="E2" t="s">
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B3" s="2">
         <v>0.8125</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -4873,130 +4867,130 @@
         <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B4" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
         <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B6" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
         <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" t="s">
-        <v>159</v>
-      </c>
       <c r="E8" t="s">
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2">
         <v>0.85416666666666663</v>
@@ -5005,21 +4999,21 @@
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B10" s="2">
         <v>0.8125</v>
@@ -5028,136 +5022,136 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
         <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B11" s="2">
         <v>0.8125</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B13" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B16" s="2">
         <v>0.8125</v>
@@ -5166,27 +5160,27 @@
         <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -5195,44 +5189,44 @@
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" t="s">
-        <v>165</v>
-      </c>
       <c r="G18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2">
         <v>0.8125</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -5241,130 +5235,130 @@
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" t="s">
-        <v>165</v>
-      </c>
       <c r="G20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C22" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>165</v>
-      </c>
       <c r="G22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B23" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
         <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B24" s="6">
         <v>0.8125</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B25" s="6">
         <v>0.85416666666666663</v>
@@ -5373,16 +5367,16 @@
         <v>56</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDDD7F3-FC82-1A41-A44A-384EBCACB8A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C840DE-66AE-E346-8BEC-3092533C12B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -651,9 +651,6 @@
     <t>20/4 一</t>
   </si>
   <si>
-    <t>豬膽 - 六六 A</t>
-  </si>
-  <si>
     <t>27/4 一</t>
   </si>
   <si>
@@ -677,6 +674,10 @@
   </si>
   <si>
     <t>中 C</t>
+  </si>
+  <si>
+    <t>豬臘 - 六六 A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3469,7 +3470,7 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="C104" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D104" t="s">
         <v>70</v>
@@ -3509,7 +3510,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B106" s="2">
         <v>0.8125</v>
@@ -3532,7 +3533,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B107" s="2">
         <v>0.8125</v>
@@ -3555,7 +3556,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B108" s="2">
         <v>0.85416666666666663</v>
@@ -3578,7 +3579,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B109" s="2">
         <v>0.85416666666666663</v>
@@ -3601,7 +3602,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B110" s="2">
         <v>0.89583333333333337</v>
@@ -3624,7 +3625,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B111" s="2">
         <v>0.89583333333333337</v>
@@ -3670,7 +3671,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B113" s="2">
         <v>0.8125</v>
@@ -3693,7 +3694,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B114" s="2">
         <v>0.8125</v>
@@ -3716,7 +3717,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B115" s="2">
         <v>0.85416666666666663</v>
@@ -3739,7 +3740,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B116" s="2">
         <v>0.85416666666666663</v>
@@ -3762,7 +3763,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B117" s="2">
         <v>0.89583333333333337</v>
@@ -3785,7 +3786,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B118" s="2">
         <v>0.89583333333333337</v>
@@ -3866,7 +3867,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G2" t="s">
         <v>145</v>
@@ -3889,7 +3890,7 @@
         <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G3" t="s">
         <v>145</v>
@@ -3912,7 +3913,7 @@
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G4" t="s">
         <v>145</v>
@@ -3935,7 +3936,7 @@
         <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G5" t="s">
         <v>145</v>
@@ -3958,7 +3959,7 @@
         <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G6" t="s">
         <v>145</v>
@@ -3981,7 +3982,7 @@
         <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G7" t="s">
         <v>145</v>
@@ -4004,7 +4005,7 @@
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G8" t="s">
         <v>145</v>
@@ -4027,7 +4028,7 @@
         <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G9" t="s">
         <v>145</v>
@@ -4050,7 +4051,7 @@
         <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G10" t="s">
         <v>145</v>
@@ -4073,7 +4074,7 @@
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G11" t="s">
         <v>145</v>
@@ -4096,7 +4097,7 @@
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G12" t="s">
         <v>145</v>
@@ -4119,7 +4120,7 @@
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G13" t="s">
         <v>145</v>
@@ -4142,7 +4143,7 @@
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G14" t="s">
         <v>145</v>
@@ -4165,7 +4166,7 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
         <v>145</v>
@@ -4188,7 +4189,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G16" t="s">
         <v>145</v>
@@ -4211,7 +4212,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G17" t="s">
         <v>145</v>
@@ -4234,7 +4235,7 @@
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G18" t="s">
         <v>145</v>
@@ -4257,7 +4258,7 @@
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G19" t="s">
         <v>145</v>
@@ -4321,7 +4322,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
         <v>145</v>
@@ -4344,7 +4345,7 @@
         <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
         <v>145</v>
@@ -4367,7 +4368,7 @@
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
         <v>145</v>
@@ -4390,7 +4391,7 @@
         <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
         <v>145</v>
@@ -4413,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G6" t="s">
         <v>145</v>
@@ -4436,7 +4437,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G7" t="s">
         <v>145</v>
@@ -4459,7 +4460,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G8" t="s">
         <v>145</v>
@@ -4482,7 +4483,7 @@
         <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G9" t="s">
         <v>145</v>
@@ -4505,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G10" t="s">
         <v>145</v>
@@ -4528,7 +4529,7 @@
         <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G11" t="s">
         <v>145</v>
@@ -4551,7 +4552,7 @@
         <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G12" t="s">
         <v>145</v>
@@ -4574,7 +4575,7 @@
         <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G13" t="s">
         <v>145</v>
@@ -4597,7 +4598,7 @@
         <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G14" t="s">
         <v>145</v>
@@ -4620,7 +4621,7 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
         <v>145</v>
@@ -4643,7 +4644,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G16" t="s">
         <v>145</v>
@@ -4666,7 +4667,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s">
         <v>145</v>
@@ -4689,7 +4690,7 @@
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G18" t="s">
         <v>145</v>
@@ -4712,7 +4713,7 @@
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
         <v>145</v>
@@ -4735,7 +4736,7 @@
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
         <v>145</v>
@@ -4758,7 +4759,7 @@
         <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
         <v>145</v>
@@ -4781,7 +4782,7 @@
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
         <v>145</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C840DE-66AE-E346-8BEC-3092533C12B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54FBF2D-0A02-2C4B-A69D-72D19A5E2C51}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="207">
   <si>
     <t>日期</t>
   </si>
@@ -677,6 +677,14 @@
   </si>
   <si>
     <t>豬臘 - 六六 A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18/4六</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25/4六</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1076,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E0EA83-C783-7140-AD8B-B43A843048C1}">
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
@@ -3349,160 +3357,160 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B99" s="2">
         <v>0.8125</v>
       </c>
       <c r="C99" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E99" t="s">
         <v>79</v>
       </c>
       <c r="F99" t="s">
-        <v>92</v>
-      </c>
-      <c r="G99" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B100" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C100" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F100" t="s">
-        <v>92</v>
-      </c>
-      <c r="G100" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B101" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C101" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D101" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E101" t="s">
         <v>79</v>
       </c>
       <c r="F101" t="s">
-        <v>93</v>
-      </c>
-      <c r="G101" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B102" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C102" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D102" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E102" t="s">
         <v>80</v>
       </c>
       <c r="F102" t="s">
-        <v>93</v>
-      </c>
-      <c r="G102" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B103" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C103" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D103" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E103" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F103" t="s">
-        <v>94</v>
-      </c>
-      <c r="G103" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B104" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="D104" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E104" t="s">
         <v>80</v>
       </c>
       <c r="F104" t="s">
-        <v>94</v>
-      </c>
-      <c r="G104" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="B105" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C105" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F105" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G105" t="s">
         <v>145</v>
@@ -3510,22 +3518,22 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B106" s="2">
         <v>0.8125</v>
       </c>
       <c r="C106" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D106" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E106" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F106" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G106" t="s">
         <v>145</v>
@@ -3533,22 +3541,22 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B107" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C107" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E107" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F107" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G107" t="s">
         <v>145</v>
@@ -3556,22 +3564,22 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B108" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C108" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="D108" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="E108" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F108" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G108" t="s">
         <v>145</v>
@@ -3579,22 +3587,22 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B109" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D109" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="E109" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F109" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G109" t="s">
         <v>145</v>
@@ -3602,22 +3610,22 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B110" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>204</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="E110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F110" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s">
         <v>145</v>
@@ -3625,22 +3633,22 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B111" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C111" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D111" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E111" t="s">
         <v>80</v>
       </c>
       <c r="F111" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G111" t="s">
         <v>145</v>
@@ -3648,162 +3656,438 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="B112" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C112" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D112" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="E112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F112" t="s">
-        <v>83</v>
-      </c>
-      <c r="G112" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B113" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D113" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E113" t="s">
         <v>79</v>
       </c>
       <c r="F113" t="s">
-        <v>83</v>
-      </c>
-      <c r="G113" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B114" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F114" t="s">
-        <v>84</v>
-      </c>
-      <c r="G114" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B115" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F115" t="s">
-        <v>84</v>
-      </c>
-      <c r="G115" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B116" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="D116" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="E116" t="s">
         <v>80</v>
       </c>
       <c r="F116" t="s">
-        <v>85</v>
-      </c>
-      <c r="G116" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B117" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D117" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="E117" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F117" t="s">
-        <v>85</v>
-      </c>
-      <c r="G117" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
+        <v>196</v>
+      </c>
+      <c r="B118" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D118" t="s">
+        <v>75</v>
+      </c>
+      <c r="E118" t="s">
+        <v>79</v>
+      </c>
+      <c r="F118" t="s">
+        <v>95</v>
+      </c>
+      <c r="G118" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>196</v>
+      </c>
+      <c r="B119" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>7</v>
+      </c>
+      <c r="E119" t="s">
+        <v>80</v>
+      </c>
+      <c r="F119" t="s">
+        <v>98</v>
+      </c>
+      <c r="G119" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>196</v>
+      </c>
+      <c r="B120" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>79</v>
+      </c>
+      <c r="F120" t="s">
+        <v>98</v>
+      </c>
+      <c r="G120" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>196</v>
+      </c>
+      <c r="B121" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C121" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" t="s">
+        <v>80</v>
+      </c>
+      <c r="F121" t="s">
+        <v>98</v>
+      </c>
+      <c r="G121" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>196</v>
+      </c>
+      <c r="B122" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s">
+        <v>79</v>
+      </c>
+      <c r="F122" t="s">
+        <v>82</v>
+      </c>
+      <c r="G122" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>196</v>
+      </c>
+      <c r="B123" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C123" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" t="s">
+        <v>80</v>
+      </c>
+      <c r="F123" t="s">
+        <v>82</v>
+      </c>
+      <c r="G123" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>162</v>
+      </c>
+      <c r="B124" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C124" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" t="s">
+        <v>80</v>
+      </c>
+      <c r="F124" t="s">
+        <v>83</v>
+      </c>
+      <c r="G124" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
         <v>197</v>
       </c>
-      <c r="B118" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="B125" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C125" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" t="s">
+        <v>79</v>
+      </c>
+      <c r="F125" t="s">
+        <v>83</v>
+      </c>
+      <c r="G125" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>197</v>
+      </c>
+      <c r="B126" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C126" t="s">
+        <v>23</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" t="s">
+        <v>80</v>
+      </c>
+      <c r="F126" t="s">
+        <v>84</v>
+      </c>
+      <c r="G126" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>197</v>
+      </c>
+      <c r="B127" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C127" t="s">
+        <v>20</v>
+      </c>
+      <c r="D127" t="s">
+        <v>21</v>
+      </c>
+      <c r="E127" t="s">
+        <v>79</v>
+      </c>
+      <c r="F127" t="s">
+        <v>84</v>
+      </c>
+      <c r="G127" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>197</v>
+      </c>
+      <c r="B128" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" t="s">
+        <v>29</v>
+      </c>
+      <c r="E128" t="s">
+        <v>80</v>
+      </c>
+      <c r="F128" t="s">
+        <v>85</v>
+      </c>
+      <c r="G128" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>197</v>
+      </c>
+      <c r="B129" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C129" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E129" t="s">
+        <v>79</v>
+      </c>
+      <c r="F129" t="s">
+        <v>85</v>
+      </c>
+      <c r="G129" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>197</v>
+      </c>
+      <c r="B130" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C130" t="s">
         <v>33</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D130" t="s">
         <v>34</v>
       </c>
-      <c r="E118" t="s">
-        <v>80</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="E130" t="s">
+        <v>80</v>
+      </c>
+      <c r="F130" t="s">
         <v>86</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G130" t="s">
         <v>145</v>
       </c>
     </row>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54FBF2D-0A02-2C4B-A69D-72D19A5E2C51}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227C87CE-DA0E-4F4C-B9F8-51A60844C353}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="208">
   <si>
     <t>日期</t>
   </si>
@@ -685,6 +685,10 @@
   </si>
   <si>
     <t>25/4六</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2110,7 +2114,7 @@
         <v>83</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2133,7 +2137,7 @@
         <v>84</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>100</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2156,7 +2160,7 @@
         <v>85</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2179,7 +2183,7 @@
         <v>83</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2202,7 +2206,7 @@
         <v>84</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2225,7 +2229,7 @@
         <v>85</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227C87CE-DA0E-4F4C-B9F8-51A60844C353}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E0103B-C877-1049-BC54-0A2FD1AD8C2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="209">
   <si>
     <t>日期</t>
   </si>
@@ -689,6 +689,10 @@
   </si>
   <si>
     <t>4-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2252,7 +2256,7 @@
         <v>86</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2275,7 +2279,7 @@
         <v>87</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2298,7 +2302,7 @@
         <v>88</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2321,7 +2325,7 @@
         <v>86</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2344,7 +2348,7 @@
         <v>87</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2367,7 +2371,7 @@
         <v>88</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E0103B-C877-1049-BC54-0A2FD1AD8C2C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F400851F-04AD-4446-B2BD-753079A1DED4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="210">
   <si>
     <t>日期</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>湖畔 - 東望洋</t>
-  </si>
-  <si>
-    <t>物價 - 創聯 A</t>
   </si>
   <si>
     <t>水電 - CEM</t>
@@ -693,6 +690,13 @@
   </si>
   <si>
     <t>5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物僱 - 創聯 A</t>
+  </si>
+  <si>
+    <t>0-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1112,10 +1116,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1124,7 +1128,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1134,7 +1138,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2">
         <v>0.8125</v>
@@ -1146,18 +1150,18 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2">
         <v>0.85416666666666663</v>
@@ -1169,18 +1173,18 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2">
         <v>0.89583333333333337</v>
@@ -1192,18 +1196,18 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2">
         <v>0.8125</v>
@@ -1215,18 +1219,18 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="2">
         <v>0.85416666666666663</v>
@@ -1238,18 +1242,18 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
@@ -1261,18 +1265,18 @@
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2">
         <v>0.8125</v>
@@ -1284,18 +1288,18 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2">
         <v>0.85416666666666663</v>
@@ -1307,18 +1311,18 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="2">
         <v>0.89583333333333337</v>
@@ -1330,18 +1334,18 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="2">
         <v>0.8125</v>
@@ -1353,18 +1357,18 @@
         <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
@@ -1376,18 +1380,18 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
@@ -1399,18 +1403,18 @@
         <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
@@ -1422,18 +1426,18 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B15" s="2">
         <v>0.85416666666666663</v>
@@ -1445,18 +1449,18 @@
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2">
         <v>0.89583333333333337</v>
@@ -1468,18 +1472,18 @@
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" s="2">
         <v>0.8125</v>
@@ -1491,18 +1495,18 @@
         <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="2">
         <v>0.85416666666666663</v>
@@ -1514,41 +1518,41 @@
         <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
         <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B20" s="2">
         <v>0.8125</v>
@@ -1560,18 +1564,18 @@
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
@@ -1583,41 +1587,41 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
         <v>56</v>
       </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23" s="2">
         <v>0.8125</v>
@@ -1629,363 +1633,363 @@
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
         <v>54</v>
       </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B25" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
         <v>59</v>
       </c>
-      <c r="D25" t="s">
-        <v>60</v>
-      </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
       </c>
       <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" t="s">
-        <v>62</v>
-      </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
         <v>66</v>
       </c>
-      <c r="D27" t="s">
-        <v>67</v>
-      </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
         <v>71</v>
       </c>
-      <c r="D28" t="s">
-        <v>72</v>
-      </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2">
         <v>0.8125</v>
       </c>
       <c r="C29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" t="s">
         <v>64</v>
       </c>
-      <c r="D29" t="s">
-        <v>65</v>
-      </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
         <v>69</v>
       </c>
-      <c r="D30" t="s">
-        <v>70</v>
-      </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
-        <v>75</v>
-      </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2">
         <v>0.8125</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B36" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
       </c>
       <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="s">
         <v>76</v>
       </c>
-      <c r="D38" t="s">
-        <v>77</v>
-      </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -1997,18 +2001,18 @@
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -2020,18 +2024,18 @@
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" s="2">
         <v>0.8125</v>
@@ -2043,18 +2047,18 @@
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2">
         <v>0.85416666666666663</v>
@@ -2066,18 +2070,18 @@
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" s="2">
         <v>0.89583333333333337</v>
@@ -2089,18 +2093,18 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B44" s="2">
         <v>0.8125</v>
@@ -2112,18 +2116,18 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B45" s="2">
         <v>0.85416666666666663</v>
@@ -2135,18 +2139,18 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2">
         <v>0.89583333333333337</v>
@@ -2158,18 +2162,18 @@
         <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="2">
         <v>0.8125</v>
@@ -2181,18 +2185,18 @@
         <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2">
         <v>0.85416666666666663</v>
@@ -2204,18 +2208,18 @@
         <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="2">
         <v>0.89583333333333337</v>
@@ -2227,18 +2231,18 @@
         <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2">
         <v>0.8125</v>
@@ -2250,18 +2254,18 @@
         <v>30</v>
       </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2">
         <v>0.85416666666666663</v>
@@ -2273,18 +2277,18 @@
         <v>35</v>
       </c>
       <c r="E51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B52" s="2">
         <v>0.89583333333333337</v>
@@ -2296,18 +2300,18 @@
         <v>40</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2">
         <v>0.8125</v>
@@ -2319,18 +2323,18 @@
         <v>32</v>
       </c>
       <c r="E53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2">
         <v>0.85416666666666663</v>
@@ -2342,18 +2346,18 @@
         <v>37</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2">
         <v>0.89583333333333337</v>
@@ -2365,18 +2369,18 @@
         <v>42</v>
       </c>
       <c r="E55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B56" s="2">
         <v>0.8125</v>
@@ -2385,67 +2389,67 @@
         <v>48</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B57" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="D57" t="s">
         <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B58" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B59" s="2">
         <v>0.8125</v>
@@ -2457,18 +2461,18 @@
         <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B60" s="2">
         <v>0.85416666666666663</v>
@@ -2480,202 +2484,202 @@
         <v>51</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B61" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C61" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" t="s">
         <v>55</v>
       </c>
-      <c r="D61" t="s">
-        <v>56</v>
-      </c>
       <c r="E61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" s="2">
         <v>0.8125</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B63" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" s="2">
         <v>0.8125</v>
       </c>
       <c r="C65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" t="s">
         <v>60</v>
       </c>
-      <c r="D65" t="s">
-        <v>61</v>
-      </c>
       <c r="E65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C66" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" t="s">
         <v>65</v>
       </c>
-      <c r="D66" t="s">
-        <v>66</v>
-      </c>
       <c r="E66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D67" t="s">
         <v>70</v>
       </c>
-      <c r="D67" t="s">
-        <v>71</v>
-      </c>
       <c r="E67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" s="2">
         <v>0.8125</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B69" s="2">
         <v>0.85416666666666663</v>
@@ -2687,18 +2691,18 @@
         <v>6</v>
       </c>
       <c r="E69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B70" s="2">
         <v>0.89583333333333337</v>
@@ -2710,41 +2714,41 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B71" s="2">
         <v>0.8125</v>
       </c>
       <c r="C71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71" t="s">
         <v>75</v>
       </c>
-      <c r="D71" t="s">
-        <v>76</v>
-      </c>
       <c r="E71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B72" s="2">
         <v>0.85416666666666663</v>
@@ -2756,18 +2760,18 @@
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B73" s="2">
         <v>0.89583333333333337</v>
@@ -2779,18 +2783,18 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B74" s="2">
         <v>0.8125</v>
@@ -2802,18 +2806,18 @@
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B75" s="2">
         <v>0.85416666666666663</v>
@@ -2825,18 +2829,18 @@
         <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B76" s="2">
         <v>0.89583333333333337</v>
@@ -2848,18 +2852,18 @@
         <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B77" s="2">
         <v>0.8125</v>
@@ -2871,18 +2875,18 @@
         <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B78" s="2">
         <v>0.85416666666666663</v>
@@ -2894,18 +2898,18 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B79" s="2">
         <v>0.89583333333333337</v>
@@ -2917,18 +2921,18 @@
         <v>25</v>
       </c>
       <c r="E79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B80" s="2">
         <v>0.8125</v>
@@ -2940,18 +2944,18 @@
         <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B81" s="2">
         <v>0.85416666666666663</v>
@@ -2963,18 +2967,18 @@
         <v>31</v>
       </c>
       <c r="E81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B82" s="2">
         <v>0.89583333333333337</v>
@@ -2986,18 +2990,18 @@
         <v>36</v>
       </c>
       <c r="E82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B83" s="2">
         <v>0.8125</v>
@@ -3009,18 +3013,18 @@
         <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B84" s="2">
         <v>0.85416666666666663</v>
@@ -3032,18 +3036,18 @@
         <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" s="2">
         <v>0.89583333333333337</v>
@@ -3055,156 +3059,156 @@
         <v>40</v>
       </c>
       <c r="E85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B86" s="2">
         <v>0.8125</v>
       </c>
       <c r="C86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B87" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B88" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B89" s="2">
         <v>0.8125</v>
       </c>
       <c r="C89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B90" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B91" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E91" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" s="2">
         <v>0.8125</v>
@@ -3216,18 +3220,18 @@
         <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" s="2">
         <v>0.85416666666666663</v>
@@ -3239,41 +3243,41 @@
         <v>45</v>
       </c>
       <c r="E93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="D94" t="s">
         <v>50</v>
       </c>
       <c r="E94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" s="2">
         <v>0.8125</v>
@@ -3282,21 +3286,21 @@
         <v>47</v>
       </c>
       <c r="D95" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B96" s="2">
         <v>0.85416666666666663</v>
@@ -3308,524 +3312,524 @@
         <v>49</v>
       </c>
       <c r="E96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F96" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B97" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F97" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B98" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F98" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B99" s="2">
         <v>0.8125</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E99" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B100" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C100" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D100" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E100" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F100" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B101" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E101" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B102" s="2">
         <v>0.8125</v>
       </c>
       <c r="C102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E102" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B103" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C103" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D103" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E103" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F103" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B104" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C104" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D104" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F104" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B105" s="2">
         <v>0.8125</v>
       </c>
       <c r="C105" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E105" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F105" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G105" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B106" s="2">
         <v>0.8125</v>
       </c>
       <c r="C106" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E106" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F106" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B107" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E107" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F107" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B108" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C108" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D108" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E108" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F108" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B109" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C109" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D109" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F109" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B110" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F110" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B111" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C111" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B112" s="2">
         <v>0.8125</v>
       </c>
       <c r="C112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B113" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F113" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B114" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B115" s="2">
         <v>0.8125</v>
       </c>
       <c r="C115" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D115" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F115" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B116" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B117" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B118" s="2">
         <v>0.8125</v>
       </c>
       <c r="C118" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D118" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E118" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B119" s="2">
         <v>0.8125</v>
@@ -3837,18 +3841,18 @@
         <v>7</v>
       </c>
       <c r="E119" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F119" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B120" s="2">
         <v>0.85416666666666663</v>
@@ -3860,18 +3864,18 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F120" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B121" s="2">
         <v>0.85416666666666663</v>
@@ -3883,18 +3887,18 @@
         <v>4</v>
       </c>
       <c r="E121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B122" s="2">
         <v>0.89583333333333337</v>
@@ -3906,18 +3910,18 @@
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F122" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G122" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B123" s="2">
         <v>0.89583333333333337</v>
@@ -3929,18 +3933,18 @@
         <v>12</v>
       </c>
       <c r="E123" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F123" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B124" s="2">
         <v>0.89583333333333337</v>
@@ -3952,18 +3956,18 @@
         <v>19</v>
       </c>
       <c r="E124" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F124" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B125" s="2">
         <v>0.8125</v>
@@ -3975,18 +3979,18 @@
         <v>17</v>
       </c>
       <c r="E125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F125" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G125" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B126" s="2">
         <v>0.8125</v>
@@ -3998,18 +4002,18 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F126" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B127" s="2">
         <v>0.85416666666666663</v>
@@ -4021,18 +4025,18 @@
         <v>21</v>
       </c>
       <c r="E127" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F127" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B128" s="2">
         <v>0.85416666666666663</v>
@@ -4044,18 +4048,18 @@
         <v>29</v>
       </c>
       <c r="E128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F128" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B129" s="2">
         <v>0.89583333333333337</v>
@@ -4067,18 +4071,18 @@
         <v>27</v>
       </c>
       <c r="E129" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F129" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B130" s="2">
         <v>0.89583333333333337</v>
@@ -4090,13 +4094,13 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F130" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4127,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -4139,35 +4143,35 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>168</v>
       </c>
-      <c r="D2" t="s">
-        <v>169</v>
-      </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2">
         <v>0.8125</v>
@@ -4176,159 +4180,159 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" t="s">
         <v>171</v>
       </c>
-      <c r="D4" t="s">
-        <v>172</v>
-      </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" t="s">
         <v>174</v>
       </c>
-      <c r="D6" t="s">
-        <v>175</v>
-      </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
         <v>176</v>
       </c>
-      <c r="D7" t="s">
-        <v>177</v>
-      </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B8" s="2">
         <v>0.8125</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C9" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C9" t="s">
-        <v>179</v>
-      </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2">
         <v>0.85416666666666663</v>
@@ -4340,110 +4344,110 @@
         <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B12" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
@@ -4452,90 +4456,90 @@
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
@@ -4544,16 +4548,16 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4582,10 +4586,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -4594,104 +4598,104 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2">
         <v>0.8125</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
         <v>182</v>
       </c>
-      <c r="D3" t="s">
-        <v>183</v>
-      </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" t="s">
         <v>184</v>
       </c>
-      <c r="D4" t="s">
-        <v>185</v>
-      </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C5" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>187</v>
       </c>
-      <c r="D5" t="s">
-        <v>188</v>
-      </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B6" s="2">
         <v>0.8125</v>
@@ -4700,136 +4704,136 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" t="s">
         <v>189</v>
       </c>
-      <c r="D7" t="s">
-        <v>190</v>
-      </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" t="s">
         <v>191</v>
       </c>
-      <c r="D8" t="s">
-        <v>192</v>
-      </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B10" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="2">
         <v>0.8125</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
@@ -4838,246 +4842,246 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B14" s="2">
         <v>0.8125</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B15" s="2">
         <v>0.8125</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2">
         <v>0.8125</v>
       </c>
       <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" t="s">
         <v>181</v>
       </c>
-      <c r="D20" t="s">
-        <v>182</v>
-      </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B22" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5105,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -5117,173 +5121,173 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>143</v>
       </c>
-      <c r="D2" t="s">
-        <v>144</v>
-      </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" s="2">
         <v>0.8125</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" t="s">
         <v>147</v>
       </c>
-      <c r="D4" t="s">
-        <v>148</v>
-      </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" t="s">
         <v>149</v>
       </c>
-      <c r="D5" t="s">
-        <v>150</v>
-      </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" t="s">
         <v>151</v>
       </c>
-      <c r="D6" t="s">
-        <v>152</v>
-      </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B7" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
         <v>153</v>
       </c>
-      <c r="D7" t="s">
-        <v>154</v>
-      </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C8" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>156</v>
       </c>
-      <c r="D8" t="s">
-        <v>157</v>
-      </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" s="2">
         <v>0.85416666666666663</v>
@@ -5292,21 +5296,21 @@
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="2">
         <v>0.8125</v>
@@ -5315,361 +5319,361 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B11" s="2">
         <v>0.8125</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2">
         <v>0.8125</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" s="2">
         <v>0.8125</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B19" s="2">
         <v>0.8125</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B21" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B22" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" s="6">
         <v>0.8125</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" s="6">
         <v>0.85416666666666663</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F400851F-04AD-4446-B2BD-753079A1DED4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E262C1-5185-154A-B66F-EF045A218741}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="211">
   <si>
     <t>日期</t>
   </si>
@@ -697,6 +697,10 @@
   </si>
   <si>
     <t>0-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2674,7 +2678,7 @@
         <v>94</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2697,7 +2701,7 @@
         <v>97</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2720,7 +2724,7 @@
         <v>97</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>99</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2743,7 +2747,7 @@
         <v>94</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2766,7 +2770,7 @@
         <v>97</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2789,7 +2793,7 @@
         <v>81</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E262C1-5185-154A-B66F-EF045A218741}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B5EBA-780C-D442-AFA2-4E461EBF3CB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="213">
   <si>
     <t>日期</t>
   </si>
@@ -701,6 +701,14 @@
   </si>
   <si>
     <t>2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2816,7 +2824,7 @@
         <v>81</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2839,7 +2847,7 @@
         <v>82</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2862,7 +2870,7 @@
         <v>83</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2885,7 +2893,7 @@
         <v>82</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2908,7 +2916,7 @@
         <v>83</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2931,7 +2939,7 @@
         <v>84</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2954,7 +2962,7 @@
         <v>84</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2977,7 +2985,7 @@
         <v>85</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3000,7 +3008,7 @@
         <v>86</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>99</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3023,7 +3031,7 @@
         <v>85</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3046,7 +3054,7 @@
         <v>86</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3069,7 +3077,7 @@
         <v>87</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B5EBA-780C-D442-AFA2-4E461EBF3CB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0A14C6-4DA2-8245-A6CF-FF6E6B5D5D93}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="214">
   <si>
     <t>日期</t>
   </si>
@@ -709,6 +709,10 @@
   </si>
   <si>
     <t>4-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16/4四</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -772,7 +776,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -792,6 +796,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3238,7 +3245,7 @@
         <v>87</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3261,7 +3268,7 @@
         <v>88</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3284,7 +3291,7 @@
         <v>89</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3307,7 +3314,7 @@
         <v>88</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3330,7 +3337,7 @@
         <v>89</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3353,12 +3360,12 @@
         <v>90</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>99</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="B98" s="2">
         <v>0.89583333333333337</v>
@@ -4177,7 +4184,7 @@
       <c r="F2" t="s">
         <v>198</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4200,7 +4207,7 @@
       <c r="F3" t="s">
         <v>199</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4223,7 +4230,7 @@
       <c r="F4" t="s">
         <v>197</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4246,7 +4253,7 @@
       <c r="F5" t="s">
         <v>199</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4269,7 +4276,7 @@
       <c r="F6" t="s">
         <v>197</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4292,7 +4299,7 @@
       <c r="F7" t="s">
         <v>199</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4315,7 +4322,7 @@
       <c r="F8" t="s">
         <v>199</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4338,7 +4345,7 @@
       <c r="F9" t="s">
         <v>197</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4361,7 +4368,7 @@
       <c r="F10" t="s">
         <v>199</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4384,7 +4391,7 @@
       <c r="F11" t="s">
         <v>197</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4407,7 +4414,7 @@
       <c r="F12" t="s">
         <v>199</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4430,7 +4437,7 @@
       <c r="F13" t="s">
         <v>197</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4453,7 +4460,7 @@
       <c r="F14" t="s">
         <v>197</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4476,7 +4483,7 @@
       <c r="F15" t="s">
         <v>199</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4499,7 +4506,7 @@
       <c r="F16" t="s">
         <v>197</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4522,7 +4529,7 @@
       <c r="F17" t="s">
         <v>199</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4545,7 +4552,7 @@
       <c r="F18" t="s">
         <v>197</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4568,7 +4575,7 @@
       <c r="F19" t="s">
         <v>199</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4632,7 +4639,7 @@
       <c r="F2" t="s">
         <v>200</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4655,7 +4662,7 @@
       <c r="F3" t="s">
         <v>200</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4678,7 +4685,7 @@
       <c r="F4" t="s">
         <v>200</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4701,7 +4708,7 @@
       <c r="F5" t="s">
         <v>201</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4724,7 +4731,7 @@
       <c r="F6" t="s">
         <v>202</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4747,7 +4754,7 @@
       <c r="F7" t="s">
         <v>201</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4770,7 +4777,7 @@
       <c r="F8" t="s">
         <v>202</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4793,7 +4800,7 @@
       <c r="F9" t="s">
         <v>201</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4816,7 +4823,7 @@
       <c r="F10" t="s">
         <v>202</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4839,7 +4846,7 @@
       <c r="F11" t="s">
         <v>202</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4862,7 +4869,7 @@
       <c r="F12" t="s">
         <v>202</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4885,7 +4892,7 @@
       <c r="F13" t="s">
         <v>202</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4908,7 +4915,7 @@
       <c r="F14" t="s">
         <v>201</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4931,7 +4938,7 @@
       <c r="F15" t="s">
         <v>200</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4954,7 +4961,7 @@
       <c r="F16" t="s">
         <v>201</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4977,7 +4984,7 @@
       <c r="F17" t="s">
         <v>200</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5000,7 +5007,7 @@
       <c r="F18" t="s">
         <v>201</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5023,7 +5030,7 @@
       <c r="F19" t="s">
         <v>200</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5046,7 +5053,7 @@
       <c r="F20" t="s">
         <v>200</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5069,7 +5076,7 @@
       <c r="F21" t="s">
         <v>200</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5092,7 +5099,7 @@
       <c r="F22" t="s">
         <v>200</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5155,8 +5162,8 @@
       <c r="F2" t="s">
         <v>162</v>
       </c>
-      <c r="G2" t="s">
-        <v>144</v>
+      <c r="G2" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5178,8 +5185,8 @@
       <c r="F3" t="s">
         <v>163</v>
       </c>
-      <c r="G3" t="s">
-        <v>144</v>
+      <c r="G3" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5201,8 +5208,8 @@
       <c r="F4" t="s">
         <v>162</v>
       </c>
-      <c r="G4" t="s">
-        <v>144</v>
+      <c r="G4" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5224,8 +5231,8 @@
       <c r="F5" t="s">
         <v>163</v>
       </c>
-      <c r="G5" t="s">
-        <v>144</v>
+      <c r="G5" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5247,8 +5254,8 @@
       <c r="F6" t="s">
         <v>162</v>
       </c>
-      <c r="G6" t="s">
-        <v>144</v>
+      <c r="G6" s="4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5270,8 +5277,8 @@
       <c r="F7" t="s">
         <v>163</v>
       </c>
-      <c r="G7" t="s">
-        <v>144</v>
+      <c r="G7" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5293,7 +5300,7 @@
       <c r="F8" t="s">
         <v>164</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5316,7 +5323,7 @@
       <c r="F9" t="s">
         <v>164</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5339,7 +5346,7 @@
       <c r="F10" t="s">
         <v>163</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5362,7 +5369,7 @@
       <c r="F11" t="s">
         <v>162</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5385,7 +5392,7 @@
       <c r="F12" t="s">
         <v>163</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5408,7 +5415,7 @@
       <c r="F13" t="s">
         <v>162</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5431,7 +5438,7 @@
       <c r="F14" t="s">
         <v>163</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5454,7 +5461,7 @@
       <c r="F15" t="s">
         <v>162</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5477,7 +5484,7 @@
       <c r="F16" t="s">
         <v>164</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5500,7 +5507,7 @@
       <c r="F17" t="s">
         <v>164</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5523,7 +5530,7 @@
       <c r="F18" t="s">
         <v>162</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5546,7 +5553,7 @@
       <c r="F19" t="s">
         <v>163</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5569,7 +5576,7 @@
       <c r="F20" t="s">
         <v>162</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5592,7 +5599,7 @@
       <c r="F21" t="s">
         <v>163</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5615,7 +5622,7 @@
       <c r="F22" t="s">
         <v>162</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5638,7 +5645,7 @@
       <c r="F23" t="s">
         <v>163</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5661,7 +5668,7 @@
       <c r="F24" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="7" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5684,7 +5691,7 @@
       <c r="F25" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="7" t="s">
         <v>144</v>
       </c>
     </row>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0A14C6-4DA2-8245-A6CF-FF6E6B5D5D93}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E851B50D-8DB4-9E49-9EF8-A0040CED134F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="217">
   <si>
     <t>日期</t>
   </si>
@@ -713,6 +713,18 @@
   </si>
   <si>
     <t>16/4四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4185,7 +4197,7 @@
         <v>198</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4208,7 +4220,7 @@
         <v>199</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4231,7 +4243,7 @@
         <v>197</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4254,7 +4266,7 @@
         <v>199</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4277,7 +4289,7 @@
         <v>197</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4300,7 +4312,7 @@
         <v>199</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>144</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E851B50D-8DB4-9E49-9EF8-A0040CED134F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0F8E8D-19B9-8849-AAE2-FC103D568C19}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="219">
   <si>
     <t>日期</t>
   </si>
@@ -725,6 +725,14 @@
   </si>
   <si>
     <t>2-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3394,8 +3402,8 @@
       <c r="F98" t="s">
         <v>90</v>
       </c>
-      <c r="G98" t="s">
-        <v>144</v>
+      <c r="G98" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3555,8 +3563,8 @@
       <c r="F105" t="s">
         <v>91</v>
       </c>
-      <c r="G105" t="s">
-        <v>144</v>
+      <c r="G105" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3578,8 +3586,8 @@
       <c r="F106" t="s">
         <v>91</v>
       </c>
-      <c r="G106" t="s">
-        <v>144</v>
+      <c r="G106" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3601,8 +3609,8 @@
       <c r="F107" t="s">
         <v>92</v>
       </c>
-      <c r="G107" t="s">
-        <v>144</v>
+      <c r="G107" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3624,8 +3632,8 @@
       <c r="F108" t="s">
         <v>92</v>
       </c>
-      <c r="G108" t="s">
-        <v>144</v>
+      <c r="G108" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3647,8 +3655,8 @@
       <c r="F109" t="s">
         <v>93</v>
       </c>
-      <c r="G109" t="s">
-        <v>144</v>
+      <c r="G109" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3670,8 +3678,8 @@
       <c r="F110" t="s">
         <v>93</v>
       </c>
-      <c r="G110" t="s">
-        <v>144</v>
+      <c r="G110" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3693,8 +3701,8 @@
       <c r="F111" t="s">
         <v>94</v>
       </c>
-      <c r="G111" t="s">
-        <v>144</v>
+      <c r="G111" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3854,8 +3862,8 @@
       <c r="F118" t="s">
         <v>94</v>
       </c>
-      <c r="G118" t="s">
-        <v>144</v>
+      <c r="G118" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3877,8 +3885,8 @@
       <c r="F119" t="s">
         <v>97</v>
       </c>
-      <c r="G119" t="s">
-        <v>144</v>
+      <c r="G119" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3900,8 +3908,8 @@
       <c r="F120" t="s">
         <v>97</v>
       </c>
-      <c r="G120" t="s">
-        <v>144</v>
+      <c r="G120" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3923,8 +3931,8 @@
       <c r="F121" t="s">
         <v>97</v>
       </c>
-      <c r="G121" t="s">
-        <v>144</v>
+      <c r="G121" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3946,8 +3954,8 @@
       <c r="F122" t="s">
         <v>81</v>
       </c>
-      <c r="G122" t="s">
-        <v>144</v>
+      <c r="G122" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3969,8 +3977,8 @@
       <c r="F123" t="s">
         <v>81</v>
       </c>
-      <c r="G123" t="s">
-        <v>144</v>
+      <c r="G123" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3992,8 +4000,8 @@
       <c r="F124" t="s">
         <v>82</v>
       </c>
-      <c r="G124" t="s">
-        <v>144</v>
+      <c r="G124" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4015,8 +4023,8 @@
       <c r="F125" t="s">
         <v>82</v>
       </c>
-      <c r="G125" t="s">
-        <v>144</v>
+      <c r="G125" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4038,8 +4046,8 @@
       <c r="F126" t="s">
         <v>83</v>
       </c>
-      <c r="G126" t="s">
-        <v>144</v>
+      <c r="G126" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4061,8 +4069,8 @@
       <c r="F127" t="s">
         <v>83</v>
       </c>
-      <c r="G127" t="s">
-        <v>144</v>
+      <c r="G127" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4084,8 +4092,8 @@
       <c r="F128" t="s">
         <v>84</v>
       </c>
-      <c r="G128" t="s">
-        <v>144</v>
+      <c r="G128" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4107,8 +4115,8 @@
       <c r="F129" t="s">
         <v>84</v>
       </c>
-      <c r="G129" t="s">
-        <v>144</v>
+      <c r="G129" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4130,8 +4138,8 @@
       <c r="F130" t="s">
         <v>85</v>
       </c>
-      <c r="G130" t="s">
-        <v>144</v>
+      <c r="G130" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4652,7 +4660,7 @@
         <v>200</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4675,7 +4683,7 @@
         <v>200</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4698,7 +4706,7 @@
         <v>200</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5313,7 +5321,7 @@
         <v>164</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5336,7 +5344,7 @@
         <v>164</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0F8E8D-19B9-8849-AAE2-FC103D568C19}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB0BE77-97BE-0F45-B53C-0DF2C21A8B68}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="220">
   <si>
     <t>日期</t>
   </si>
@@ -733,6 +733,10 @@
   </si>
   <si>
     <t>5-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4729,7 +4733,7 @@
         <v>201</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4752,7 +4756,7 @@
         <v>202</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4775,7 +4779,7 @@
         <v>201</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4798,7 +4802,7 @@
         <v>202</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4821,7 +4825,7 @@
         <v>201</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4844,7 +4848,7 @@
         <v>202</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB0BE77-97BE-0F45-B53C-0DF2C21A8B68}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AFED6E-D823-F74A-9C92-AC44DE69D81C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="221">
   <si>
     <t>日期</t>
   </si>
@@ -737,6 +737,10 @@
   </si>
   <si>
     <t>9-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3568,7 +3572,7 @@
         <v>91</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>99</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3591,7 +3595,7 @@
         <v>91</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3614,7 +3618,7 @@
         <v>92</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3637,7 +3641,7 @@
         <v>92</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3660,7 +3664,7 @@
         <v>93</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>99</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3683,7 +3687,7 @@
         <v>93</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AFED6E-D823-F74A-9C92-AC44DE69D81C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B583E5-F2E5-5646-953B-A614568C81E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="224">
   <si>
     <t>日期</t>
   </si>
@@ -741,6 +741,18 @@
   </si>
   <si>
     <t>7-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4351,7 +4363,7 @@
         <v>199</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4374,7 +4386,7 @@
         <v>197</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>144</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4397,7 +4409,7 @@
         <v>199</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4420,7 +4432,7 @@
         <v>197</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>144</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4443,7 +4455,7 @@
         <v>199</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4466,7 +4478,7 @@
         <v>197</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5375,7 +5387,7 @@
         <v>163</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5398,7 +5410,7 @@
         <v>162</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5421,7 +5433,7 @@
         <v>163</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5444,7 +5456,7 @@
         <v>162</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5467,7 +5479,7 @@
         <v>163</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5490,7 +5502,7 @@
         <v>162</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B583E5-F2E5-5646-953B-A614568C81E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963AC016-2CF3-9D46-99D5-42243E2CAD37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="253">
   <si>
     <t>日期</t>
   </si>
@@ -754,6 +754,103 @@
   <si>
     <t>2-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/5 二</t>
+  </si>
+  <si>
+    <t>公務 - 紅鐵</t>
+  </si>
+  <si>
+    <t>6/5 三</t>
+  </si>
+  <si>
+    <t>元 C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元 B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初 F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高 B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公務 - 紅纖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/5 六</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>11/5 一</t>
+  </si>
+  <si>
+    <t>12/5 二</t>
+  </si>
+  <si>
+    <t>13/5 三</t>
+  </si>
+  <si>
+    <t>元 A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14/5 四</t>
+  </si>
+  <si>
+    <t>15/5 五</t>
+  </si>
+  <si>
+    <t>麵飽 - PAPAPA</t>
+  </si>
+  <si>
+    <t>麵飽 - PAPA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中 C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中 B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中 A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16/5 六</t>
+  </si>
+  <si>
+    <t>18/5 一</t>
+  </si>
+  <si>
+    <t>豬膶 - 六六 A</t>
+  </si>
+  <si>
+    <t>19/5 二</t>
+  </si>
+  <si>
+    <t>豬膶 - QUU</t>
+  </si>
+  <si>
+    <t>20/5 三</t>
+  </si>
+  <si>
+    <t>21/5 四</t>
+  </si>
+  <si>
+    <t>22/5 五</t>
   </si>
 </sst>
 </file>
@@ -1155,16 +1252,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E0EA83-C783-7140-AD8B-B43A843048C1}">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -4116,7 +4212,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:15">
       <c r="A129" t="s">
         <v>196</v>
       </c>
@@ -4139,7 +4235,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:15">
       <c r="A130" t="s">
         <v>196</v>
       </c>
@@ -4160,6 +4256,917 @@
       </c>
       <c r="G130" s="4" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131" t="s">
+        <v>224</v>
+      </c>
+      <c r="B131" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C131" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" t="s">
+        <v>32</v>
+      </c>
+      <c r="E131" t="s">
+        <v>78</v>
+      </c>
+      <c r="F131" t="s">
+        <v>229</v>
+      </c>
+      <c r="G131" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B132" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C132" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" t="s">
+        <v>32</v>
+      </c>
+      <c r="E132" t="s">
+        <v>78</v>
+      </c>
+      <c r="F132" t="s">
+        <v>229</v>
+      </c>
+      <c r="G132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133" t="s">
+        <v>232</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C133" t="s">
+        <v>80</v>
+      </c>
+      <c r="D133" t="s">
+        <v>80</v>
+      </c>
+      <c r="E133" t="s">
+        <v>78</v>
+      </c>
+      <c r="F133" t="s">
+        <v>233</v>
+      </c>
+      <c r="G133" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134" t="s">
+        <v>232</v>
+      </c>
+      <c r="B134" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C134" t="s">
+        <v>80</v>
+      </c>
+      <c r="D134" t="s">
+        <v>80</v>
+      </c>
+      <c r="E134" t="s">
+        <v>79</v>
+      </c>
+      <c r="F134" t="s">
+        <v>233</v>
+      </c>
+      <c r="G134" t="s">
+        <v>144</v>
+      </c>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+      <c r="N134" s="1"/>
+      <c r="O134" s="1"/>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135" t="s">
+        <v>232</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C135" t="s">
+        <v>80</v>
+      </c>
+      <c r="D135" t="s">
+        <v>80</v>
+      </c>
+      <c r="E135" t="s">
+        <v>78</v>
+      </c>
+      <c r="F135" t="s">
+        <v>233</v>
+      </c>
+      <c r="G135" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C136" t="s">
+        <v>80</v>
+      </c>
+      <c r="D136" t="s">
+        <v>80</v>
+      </c>
+      <c r="E136" t="s">
+        <v>79</v>
+      </c>
+      <c r="F136" t="s">
+        <v>233</v>
+      </c>
+      <c r="G136" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137" t="s">
+        <v>232</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C137" t="s">
+        <v>80</v>
+      </c>
+      <c r="D137" t="s">
+        <v>80</v>
+      </c>
+      <c r="E137" t="s">
+        <v>78</v>
+      </c>
+      <c r="F137" t="s">
+        <v>233</v>
+      </c>
+      <c r="G137" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138" t="s">
+        <v>232</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C138" t="s">
+        <v>80</v>
+      </c>
+      <c r="D138" t="s">
+        <v>80</v>
+      </c>
+      <c r="E138" t="s">
+        <v>79</v>
+      </c>
+      <c r="F138" t="s">
+        <v>233</v>
+      </c>
+      <c r="G138" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139" t="s">
+        <v>234</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C139" t="s">
+        <v>40</v>
+      </c>
+      <c r="D139" t="s">
+        <v>42</v>
+      </c>
+      <c r="E139" t="s">
+        <v>78</v>
+      </c>
+      <c r="F139" t="s">
+        <v>87</v>
+      </c>
+      <c r="G139" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140" t="s">
+        <v>234</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C140" t="s">
+        <v>47</v>
+      </c>
+      <c r="D140" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" t="s">
+        <v>79</v>
+      </c>
+      <c r="F140" t="s">
+        <v>88</v>
+      </c>
+      <c r="G140" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141" t="s">
+        <v>234</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C141" t="s">
+        <v>169</v>
+      </c>
+      <c r="D141" t="s">
+        <v>46</v>
+      </c>
+      <c r="E141" t="s">
+        <v>78</v>
+      </c>
+      <c r="F141" t="s">
+        <v>88</v>
+      </c>
+      <c r="G141" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142" t="s">
+        <v>234</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C142" t="s">
+        <v>52</v>
+      </c>
+      <c r="D142" t="s">
+        <v>208</v>
+      </c>
+      <c r="E142" t="s">
+        <v>79</v>
+      </c>
+      <c r="F142" t="s">
+        <v>89</v>
+      </c>
+      <c r="G142" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
+      <c r="A143" t="s">
+        <v>234</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C143" t="s">
+        <v>49</v>
+      </c>
+      <c r="D143" t="s">
+        <v>51</v>
+      </c>
+      <c r="E143" t="s">
+        <v>78</v>
+      </c>
+      <c r="F143" t="s">
+        <v>89</v>
+      </c>
+      <c r="G143" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144" t="s">
+        <v>234</v>
+      </c>
+      <c r="B144" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C144" t="s">
+        <v>56</v>
+      </c>
+      <c r="D144" t="s">
+        <v>57</v>
+      </c>
+      <c r="E144" t="s">
+        <v>79</v>
+      </c>
+      <c r="F144" t="s">
+        <v>90</v>
+      </c>
+      <c r="G144" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>238</v>
+      </c>
+      <c r="B145" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C145" t="s">
+        <v>53</v>
+      </c>
+      <c r="D145" t="s">
+        <v>55</v>
+      </c>
+      <c r="E145" t="s">
+        <v>79</v>
+      </c>
+      <c r="F145" t="s">
+        <v>90</v>
+      </c>
+      <c r="G145" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>245</v>
+      </c>
+      <c r="B146" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C146" t="s">
+        <v>80</v>
+      </c>
+      <c r="D146" t="s">
+        <v>80</v>
+      </c>
+      <c r="E146" t="s">
+        <v>78</v>
+      </c>
+      <c r="F146" t="s">
+        <v>233</v>
+      </c>
+      <c r="G146" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>245</v>
+      </c>
+      <c r="B147" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C147" t="s">
+        <v>80</v>
+      </c>
+      <c r="D147" t="s">
+        <v>80</v>
+      </c>
+      <c r="E147" t="s">
+        <v>79</v>
+      </c>
+      <c r="F147" t="s">
+        <v>233</v>
+      </c>
+      <c r="G147" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" t="s">
+        <v>245</v>
+      </c>
+      <c r="B148" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C148" t="s">
+        <v>80</v>
+      </c>
+      <c r="D148" t="s">
+        <v>80</v>
+      </c>
+      <c r="E148" t="s">
+        <v>78</v>
+      </c>
+      <c r="F148" t="s">
+        <v>233</v>
+      </c>
+      <c r="G148" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149" t="s">
+        <v>245</v>
+      </c>
+      <c r="B149" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C149" t="s">
+        <v>80</v>
+      </c>
+      <c r="D149" t="s">
+        <v>80</v>
+      </c>
+      <c r="E149" t="s">
+        <v>79</v>
+      </c>
+      <c r="F149" t="s">
+        <v>233</v>
+      </c>
+      <c r="G149" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150" t="s">
+        <v>245</v>
+      </c>
+      <c r="B150" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C150" t="s">
+        <v>80</v>
+      </c>
+      <c r="D150" t="s">
+        <v>80</v>
+      </c>
+      <c r="E150" t="s">
+        <v>78</v>
+      </c>
+      <c r="F150" t="s">
+        <v>233</v>
+      </c>
+      <c r="G150" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151" t="s">
+        <v>245</v>
+      </c>
+      <c r="B151" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C151" t="s">
+        <v>80</v>
+      </c>
+      <c r="D151" t="s">
+        <v>80</v>
+      </c>
+      <c r="E151" t="s">
+        <v>79</v>
+      </c>
+      <c r="F151" t="s">
+        <v>233</v>
+      </c>
+      <c r="G151" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" t="s">
+        <v>246</v>
+      </c>
+      <c r="B152" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C152" t="s">
+        <v>61</v>
+      </c>
+      <c r="D152" t="s">
+        <v>62</v>
+      </c>
+      <c r="E152" t="s">
+        <v>78</v>
+      </c>
+      <c r="F152" t="s">
+        <v>91</v>
+      </c>
+      <c r="G152" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" t="s">
+        <v>246</v>
+      </c>
+      <c r="B153" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C153" t="s">
+        <v>58</v>
+      </c>
+      <c r="D153" t="s">
+        <v>60</v>
+      </c>
+      <c r="E153" t="s">
+        <v>79</v>
+      </c>
+      <c r="F153" t="s">
+        <v>91</v>
+      </c>
+      <c r="G153" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154" t="s">
+        <v>246</v>
+      </c>
+      <c r="B154" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C154" t="s">
+        <v>66</v>
+      </c>
+      <c r="D154" t="s">
+        <v>67</v>
+      </c>
+      <c r="E154" t="s">
+        <v>78</v>
+      </c>
+      <c r="F154" t="s">
+        <v>92</v>
+      </c>
+      <c r="G154" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155" t="s">
+        <v>246</v>
+      </c>
+      <c r="B155" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C155" t="s">
+        <v>63</v>
+      </c>
+      <c r="D155" t="s">
+        <v>65</v>
+      </c>
+      <c r="E155" t="s">
+        <v>79</v>
+      </c>
+      <c r="F155" t="s">
+        <v>92</v>
+      </c>
+      <c r="G155" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156" t="s">
+        <v>246</v>
+      </c>
+      <c r="B156" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C156" t="s">
+        <v>71</v>
+      </c>
+      <c r="D156" t="s">
+        <v>247</v>
+      </c>
+      <c r="E156" t="s">
+        <v>78</v>
+      </c>
+      <c r="F156" t="s">
+        <v>93</v>
+      </c>
+      <c r="G156" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
+      <c r="A157" t="s">
+        <v>246</v>
+      </c>
+      <c r="B157" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>70</v>
+      </c>
+      <c r="E157" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157" t="s">
+        <v>93</v>
+      </c>
+      <c r="G157" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
+      <c r="A158" t="s">
+        <v>248</v>
+      </c>
+      <c r="B158" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C158" t="s">
+        <v>76</v>
+      </c>
+      <c r="D158" t="s">
+        <v>77</v>
+      </c>
+      <c r="E158" t="s">
+        <v>78</v>
+      </c>
+      <c r="F158" t="s">
+        <v>94</v>
+      </c>
+      <c r="G158" t="s">
+        <v>144</v>
+      </c>
+      <c r="J158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+      <c r="N158" s="1"/>
+      <c r="O158" s="1"/>
+      <c r="P158" s="1"/>
+    </row>
+    <row r="159" spans="1:16">
+      <c r="A159" t="s">
+        <v>248</v>
+      </c>
+      <c r="B159" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C159" t="s">
+        <v>73</v>
+      </c>
+      <c r="D159" t="s">
+        <v>75</v>
+      </c>
+      <c r="E159" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" t="s">
+        <v>94</v>
+      </c>
+      <c r="G159" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
+      <c r="A160" t="s">
+        <v>248</v>
+      </c>
+      <c r="B160" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>4</v>
+      </c>
+      <c r="E160" t="s">
+        <v>78</v>
+      </c>
+      <c r="F160" t="s">
+        <v>97</v>
+      </c>
+      <c r="G160" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>248</v>
+      </c>
+      <c r="B161" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" t="s">
+        <v>6</v>
+      </c>
+      <c r="E161" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161" t="s">
+        <v>97</v>
+      </c>
+      <c r="G161" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>248</v>
+      </c>
+      <c r="B162" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" t="s">
+        <v>78</v>
+      </c>
+      <c r="F162" t="s">
+        <v>97</v>
+      </c>
+      <c r="G162" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>248</v>
+      </c>
+      <c r="B163" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C163" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" t="s">
+        <v>249</v>
+      </c>
+      <c r="E163" t="s">
+        <v>79</v>
+      </c>
+      <c r="F163" t="s">
+        <v>81</v>
+      </c>
+      <c r="G163" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>250</v>
+      </c>
+      <c r="B164" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C164" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" t="s">
+        <v>79</v>
+      </c>
+      <c r="F164" t="s">
+        <v>81</v>
+      </c>
+      <c r="G164" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>250</v>
+      </c>
+      <c r="B165" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" t="s">
+        <v>79</v>
+      </c>
+      <c r="F165" t="s">
+        <v>82</v>
+      </c>
+      <c r="G165" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>250</v>
+      </c>
+      <c r="B166" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C166" t="s">
+        <v>16</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="s">
+        <v>79</v>
+      </c>
+      <c r="F166" t="s">
+        <v>82</v>
+      </c>
+      <c r="G166" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>252</v>
+      </c>
+      <c r="B167" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C167" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" t="s">
+        <v>24</v>
+      </c>
+      <c r="E167" t="s">
+        <v>79</v>
+      </c>
+      <c r="F167" t="s">
+        <v>83</v>
+      </c>
+      <c r="G167" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>252</v>
+      </c>
+      <c r="B168" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C168" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" t="s">
+        <v>79</v>
+      </c>
+      <c r="F168" t="s">
+        <v>83</v>
+      </c>
+      <c r="G168" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>252</v>
+      </c>
+      <c r="B169" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" t="s">
+        <v>29</v>
+      </c>
+      <c r="E169" t="s">
+        <v>79</v>
+      </c>
+      <c r="F169" t="s">
+        <v>84</v>
+      </c>
+      <c r="G169" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4171,7 +5178,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A652382C-1B8E-3D47-8B07-5935E173CD82}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -4619,6 +5626,489 @@
         <v>144</v>
       </c>
     </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" t="s">
+        <v>230</v>
+      </c>
+      <c r="G20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s">
+        <v>198</v>
+      </c>
+      <c r="G21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" t="s">
+        <v>198</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>198</v>
+      </c>
+      <c r="G27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C29" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C31" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" t="s">
+        <v>198</v>
+      </c>
+      <c r="G31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" t="s">
+        <v>230</v>
+      </c>
+      <c r="G33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C35" t="s">
+        <v>169</v>
+      </c>
+      <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" t="s">
+        <v>230</v>
+      </c>
+      <c r="G35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C36" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" t="s">
+        <v>230</v>
+      </c>
+      <c r="G37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>250</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>250</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C39" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" t="s">
+        <v>198</v>
+      </c>
+      <c r="G39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
+        <v>198</v>
+      </c>
+      <c r="G40" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4627,7 +6117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B38FBF-5FEC-5740-9062-B8355DB1F4DA}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5005,7 +6495,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -5028,7 +6518,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -5051,7 +6541,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -5074,7 +6564,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>161</v>
       </c>
@@ -5097,7 +6587,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:17">
       <c r="A21" t="s">
         <v>161</v>
       </c>
@@ -5120,7 +6610,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>161</v>
       </c>
@@ -5140,6 +6630,427 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>238</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" t="s">
+        <v>242</v>
+      </c>
+      <c r="G25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>243</v>
+      </c>
+      <c r="G26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>244</v>
+      </c>
+      <c r="G27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C29" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>244</v>
+      </c>
+      <c r="G29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" t="s">
+        <v>243</v>
+      </c>
+      <c r="G30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" t="s">
+        <v>239</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" t="s">
+        <v>144</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>251</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" t="s">
+        <v>244</v>
+      </c>
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" t="s">
+        <v>243</v>
+      </c>
+      <c r="G35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>244</v>
+      </c>
+      <c r="G36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>251</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" t="s">
+        <v>243</v>
+      </c>
+      <c r="G37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>252</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" t="s">
+        <v>242</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>252</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" t="s">
+        <v>242</v>
+      </c>
+      <c r="G39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>252</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G40" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5151,7 +7062,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F9B54F-1C5B-D04D-993A-929D11ED7A52}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5160,7 +7071,7 @@
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5183,7 +7094,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>141</v>
       </c>
@@ -5205,8 +7116,15 @@
       <c r="G2" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>141</v>
       </c>
@@ -5229,7 +7147,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -5252,7 +7170,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>141</v>
       </c>
@@ -5275,7 +7193,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -5298,7 +7216,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -5321,7 +7239,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -5344,7 +7262,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>154</v>
       </c>
@@ -5367,7 +7285,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -5390,7 +7308,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>158</v>
       </c>
@@ -5413,7 +7331,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>158</v>
       </c>
@@ -5436,7 +7354,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>158</v>
       </c>
@@ -5459,7 +7377,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>158</v>
       </c>
@@ -5482,7 +7400,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>158</v>
       </c>
@@ -5505,7 +7423,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -5528,7 +7446,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>159</v>
       </c>
@@ -5551,7 +7469,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>160</v>
       </c>
@@ -5574,7 +7492,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>160</v>
       </c>
@@ -5597,7 +7515,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>160</v>
       </c>
@@ -5620,7 +7538,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>160</v>
       </c>
@@ -5643,7 +7561,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -5666,7 +7584,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>160</v>
       </c>
@@ -5689,7 +7607,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:16">
       <c r="A24" s="5" t="s">
         <v>161</v>
       </c>
@@ -5712,7 +7630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:16">
       <c r="A25" s="5" t="s">
         <v>161</v>
       </c>
@@ -5732,6 +7650,427 @@
         <v>164</v>
       </c>
       <c r="G25" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>227</v>
+      </c>
+      <c r="G26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>224</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>228</v>
+      </c>
+      <c r="G27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C29" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>228</v>
+      </c>
+      <c r="G29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C30" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" t="s">
+        <v>228</v>
+      </c>
+      <c r="G30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G32" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" t="s">
+        <v>227</v>
+      </c>
+      <c r="G33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C34" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" t="s">
+        <v>228</v>
+      </c>
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" t="s">
+        <v>228</v>
+      </c>
+      <c r="G35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>237</v>
+      </c>
+      <c r="G36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" t="s">
+        <v>237</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" t="s">
+        <v>228</v>
+      </c>
+      <c r="G39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
+        <v>237</v>
+      </c>
+      <c r="G40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" t="s">
+        <v>228</v>
+      </c>
+      <c r="G41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F42" t="s">
+        <v>227</v>
+      </c>
+      <c r="G42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C43" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" t="s">
         <v>144</v>
       </c>
     </row>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963AC016-2CF3-9D46-99D5-42243E2CAD37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D7F3A6-E65F-0749-ACBF-45F3F7AD5783}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="251">
   <si>
     <t>日期</t>
   </si>
@@ -788,9 +788,6 @@
     <t>9/5 六</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>11/5 一</t>
   </si>
   <si>
@@ -808,9 +805,6 @@
   </si>
   <si>
     <t>15/5 五</t>
-  </si>
-  <si>
-    <t>麵飽 - PAPAPA</t>
   </si>
   <si>
     <t>麵飽 - PAPA</t>
@@ -4321,7 +4315,7 @@
         <v>78</v>
       </c>
       <c r="F133" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s">
         <v>144</v>
@@ -4344,7 +4338,7 @@
         <v>79</v>
       </c>
       <c r="F134" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s">
         <v>144</v>
@@ -4374,7 +4368,7 @@
         <v>78</v>
       </c>
       <c r="F135" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G135" t="s">
         <v>144</v>
@@ -4397,7 +4391,7 @@
         <v>79</v>
       </c>
       <c r="F136" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G136" t="s">
         <v>144</v>
@@ -4420,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="F137" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s">
         <v>144</v>
@@ -4443,7 +4437,7 @@
         <v>79</v>
       </c>
       <c r="F138" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s">
         <v>144</v>
@@ -4451,7 +4445,7 @@
     </row>
     <row r="139" spans="1:15">
       <c r="A139" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B139" s="2">
         <v>0.8125</v>
@@ -4474,7 +4468,7 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B140" s="2">
         <v>0.8125</v>
@@ -4497,7 +4491,7 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B141" s="2">
         <v>0.85416666666666663</v>
@@ -4520,7 +4514,7 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B142" s="2">
         <v>0.85416666666666663</v>
@@ -4543,7 +4537,7 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B143" s="2">
         <v>0.89583333333333337</v>
@@ -4566,7 +4560,7 @@
     </row>
     <row r="144" spans="1:15">
       <c r="A144" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B144" s="2">
         <v>0.89583333333333337</v>
@@ -4589,7 +4583,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B145" s="2">
         <v>0.89583333333333337</v>
@@ -4612,7 +4606,7 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B146" s="2">
         <v>0.8125</v>
@@ -4627,7 +4621,7 @@
         <v>78</v>
       </c>
       <c r="F146" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s">
         <v>144</v>
@@ -4635,7 +4629,7 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B147" s="2">
         <v>0.8125</v>
@@ -4650,7 +4644,7 @@
         <v>79</v>
       </c>
       <c r="F147" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G147" t="s">
         <v>144</v>
@@ -4658,7 +4652,7 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B148" s="2">
         <v>0.85416666666666663</v>
@@ -4673,7 +4667,7 @@
         <v>78</v>
       </c>
       <c r="F148" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G148" t="s">
         <v>144</v>
@@ -4681,7 +4675,7 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B149" s="2">
         <v>0.85416666666666663</v>
@@ -4696,7 +4690,7 @@
         <v>79</v>
       </c>
       <c r="F149" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G149" t="s">
         <v>144</v>
@@ -4704,7 +4698,7 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B150" s="2">
         <v>0.89583333333333337</v>
@@ -4719,7 +4713,7 @@
         <v>78</v>
       </c>
       <c r="F150" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G150" t="s">
         <v>144</v>
@@ -4727,7 +4721,7 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B151" s="2">
         <v>0.89583333333333337</v>
@@ -4742,7 +4736,7 @@
         <v>79</v>
       </c>
       <c r="F151" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s">
         <v>144</v>
@@ -4750,7 +4744,7 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B152" s="2">
         <v>0.8125</v>
@@ -4773,7 +4767,7 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B153" s="2">
         <v>0.8125</v>
@@ -4796,7 +4790,7 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B154" s="2">
         <v>0.85416666666666663</v>
@@ -4819,7 +4813,7 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B155" s="2">
         <v>0.85416666666666663</v>
@@ -4842,7 +4836,7 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B156" s="2">
         <v>0.89583333333333337</v>
@@ -4851,7 +4845,7 @@
         <v>71</v>
       </c>
       <c r="D156" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E156" t="s">
         <v>78</v>
@@ -4865,7 +4859,7 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B157" s="2">
         <v>0.89583333333333337</v>
@@ -4888,7 +4882,7 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B158" s="2">
         <v>0.8125</v>
@@ -4918,7 +4912,7 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B159" s="2">
         <v>0.8125</v>
@@ -4941,7 +4935,7 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B160" s="2">
         <v>0.85416666666666663</v>
@@ -4964,7 +4958,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B161" s="2">
         <v>0.85416666666666663</v>
@@ -4987,7 +4981,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B162" s="2">
         <v>0.89583333333333337</v>
@@ -5010,7 +5004,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B163" s="2">
         <v>0.89583333333333337</v>
@@ -5019,7 +5013,7 @@
         <v>12</v>
       </c>
       <c r="D163" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E163" t="s">
         <v>79</v>
@@ -5033,7 +5027,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B164" s="2">
         <v>0.8125</v>
@@ -5056,7 +5050,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B165" s="2">
         <v>0.85416666666666663</v>
@@ -5079,7 +5073,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B166" s="2">
         <v>0.89583333333333337</v>
@@ -5102,7 +5096,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B167" s="2">
         <v>0.8125</v>
@@ -5125,7 +5119,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B168" s="2">
         <v>0.85416666666666663</v>
@@ -5148,7 +5142,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B169" s="2">
         <v>0.89583333333333337</v>
@@ -5904,7 +5898,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
@@ -5927,7 +5921,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B33" s="2">
         <v>0.8125</v>
@@ -5950,7 +5944,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" s="2">
         <v>0.85416666666666663</v>
@@ -5973,7 +5967,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B35" s="2">
         <v>0.85416666666666663</v>
@@ -5996,7 +5990,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B36" s="2">
         <v>0.89583333333333337</v>
@@ -6019,7 +6013,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
@@ -6042,7 +6036,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -6065,7 +6059,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -6088,7 +6082,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -6635,7 +6629,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" s="2">
         <v>0.8125</v>
@@ -6650,7 +6644,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G23" t="s">
         <v>144</v>
@@ -6658,7 +6652,7 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="2">
         <v>0.85416666666666663</v>
@@ -6673,7 +6667,7 @@
         <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G24" t="s">
         <v>144</v>
@@ -6681,7 +6675,7 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" s="2">
         <v>0.89583333333333337</v>
@@ -6696,7 +6690,7 @@
         <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G25" t="s">
         <v>144</v>
@@ -6704,7 +6698,7 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
@@ -6719,7 +6713,7 @@
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G26" t="s">
         <v>144</v>
@@ -6727,7 +6721,7 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B27" s="2">
         <v>0.8125</v>
@@ -6742,7 +6736,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G27" t="s">
         <v>144</v>
@@ -6750,7 +6744,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" s="2">
         <v>0.85416666666666663</v>
@@ -6759,13 +6753,13 @@
         <v>188</v>
       </c>
       <c r="D28" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
         <v>241</v>
-      </c>
-      <c r="E28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" t="s">
-        <v>243</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
@@ -6773,7 +6767,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B29" s="2">
         <v>0.85416666666666663</v>
@@ -6788,7 +6782,7 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G29" t="s">
         <v>144</v>
@@ -6796,7 +6790,7 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B30" s="2">
         <v>0.89583333333333337</v>
@@ -6811,7 +6805,7 @@
         <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G30" t="s">
         <v>144</v>
@@ -6819,7 +6813,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
@@ -6834,7 +6828,7 @@
         <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G31" t="s">
         <v>144</v>
@@ -6842,7 +6836,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
@@ -6857,7 +6851,7 @@
         <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G32" t="s">
         <v>144</v>
@@ -6872,13 +6866,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B33" s="2">
         <v>0.8125</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -6887,7 +6881,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
@@ -6895,7 +6889,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B34" s="2">
         <v>0.85416666666666663</v>
@@ -6910,7 +6904,7 @@
         <v>78</v>
       </c>
       <c r="F34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G34" t="s">
         <v>144</v>
@@ -6918,7 +6912,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B35" s="2">
         <v>0.85416666666666663</v>
@@ -6933,7 +6927,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G35" t="s">
         <v>144</v>
@@ -6941,7 +6935,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B36" s="2">
         <v>0.89583333333333337</v>
@@ -6956,7 +6950,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -6964,7 +6958,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
@@ -6979,7 +6973,7 @@
         <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G37" t="s">
         <v>144</v>
@@ -6987,7 +6981,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -7002,7 +6996,7 @@
         <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G38" t="s">
         <v>144</v>
@@ -7010,7 +7004,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -7025,7 +7019,7 @@
         <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G39" t="s">
         <v>144</v>
@@ -7033,7 +7027,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -7048,7 +7042,7 @@
         <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G40" t="s">
         <v>144</v>
@@ -7892,7 +7886,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B36" s="2">
         <v>0.8125</v>
@@ -7907,7 +7901,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -7915,7 +7909,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B37" s="2">
         <v>0.8125</v>
@@ -7938,7 +7932,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B38" s="2">
         <v>0.85416666666666663</v>
@@ -7953,7 +7947,7 @@
         <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G38" t="s">
         <v>144</v>
@@ -7961,7 +7955,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -7984,7 +7978,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -7999,7 +7993,7 @@
         <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G40" t="s">
         <v>144</v>
@@ -8007,7 +8001,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B41" s="2">
         <v>0.89583333333333337</v>
@@ -8030,7 +8024,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2">
         <v>0.8125</v>
@@ -8053,7 +8047,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B43" s="2">
         <v>0.85416666666666663</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D7F3A6-E65F-0749-ACBF-45F3F7AD5783}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BAE492-3936-E940-A1E0-8A7EF8A05275}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="250">
   <si>
     <t>日期</t>
   </si>
@@ -829,15 +829,9 @@
     <t>18/5 一</t>
   </si>
   <si>
-    <t>豬膶 - 六六 A</t>
-  </si>
-  <si>
     <t>19/5 二</t>
   </si>
   <si>
-    <t>豬膶 - QUU</t>
-  </si>
-  <si>
     <t>20/5 三</t>
   </si>
   <si>
@@ -845,6 +839,10 @@
   </si>
   <si>
     <t>22/5 五</t>
+  </si>
+  <si>
+    <t>豬臘 - QU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4845,7 +4843,7 @@
         <v>71</v>
       </c>
       <c r="D156" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="E156" t="s">
         <v>78</v>
@@ -4882,7 +4880,7 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B158" s="2">
         <v>0.8125</v>
@@ -4912,7 +4910,7 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B159" s="2">
         <v>0.8125</v>
@@ -4935,7 +4933,7 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B160" s="2">
         <v>0.85416666666666663</v>
@@ -4958,7 +4956,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B161" s="2">
         <v>0.85416666666666663</v>
@@ -4981,7 +4979,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B162" s="2">
         <v>0.89583333333333337</v>
@@ -5004,7 +5002,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B163" s="2">
         <v>0.89583333333333337</v>
@@ -5013,7 +5011,7 @@
         <v>12</v>
       </c>
       <c r="D163" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E163" t="s">
         <v>79</v>
@@ -5027,7 +5025,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B164" s="2">
         <v>0.8125</v>
@@ -5050,7 +5048,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B165" s="2">
         <v>0.85416666666666663</v>
@@ -5073,7 +5071,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B166" s="2">
         <v>0.89583333333333337</v>
@@ -5096,7 +5094,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B167" s="2">
         <v>0.8125</v>
@@ -5119,7 +5117,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B168" s="2">
         <v>0.85416666666666663</v>
@@ -5142,7 +5140,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B169" s="2">
         <v>0.89583333333333337</v>
@@ -6036,7 +6034,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -6059,7 +6057,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -6082,7 +6080,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -6836,7 +6834,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
@@ -6866,7 +6864,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B33" s="2">
         <v>0.8125</v>
@@ -6889,7 +6887,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B34" s="2">
         <v>0.85416666666666663</v>
@@ -6912,7 +6910,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2">
         <v>0.85416666666666663</v>
@@ -6935,7 +6933,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B36" s="2">
         <v>0.89583333333333337</v>
@@ -6958,7 +6956,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
@@ -6981,7 +6979,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -7004,7 +7002,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -7027,7 +7025,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BAE492-3936-E940-A1E0-8A7EF8A05275}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6CBA20-2649-6D47-9092-D1D97CA381FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="249">
   <si>
     <t>日期</t>
   </si>
@@ -757,9 +757,6 @@
   </si>
   <si>
     <t>5/5 二</t>
-  </si>
-  <si>
-    <t>公務 - 紅鐵</t>
   </si>
   <si>
     <t>6/5 三</t>
@@ -4267,7 +4264,7 @@
         <v>78</v>
       </c>
       <c r="F131" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G131" t="s">
         <v>144</v>
@@ -4290,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="F132" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G132" t="s">
         <v>144</v>
@@ -4298,7 +4295,7 @@
     </row>
     <row r="133" spans="1:15">
       <c r="A133" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B133" s="2">
         <v>0.8125</v>
@@ -4321,7 +4318,7 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B134" s="2">
         <v>0.8125</v>
@@ -4351,7 +4348,7 @@
     </row>
     <row r="135" spans="1:15">
       <c r="A135" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B135" s="2">
         <v>0.85416666666666663</v>
@@ -4374,7 +4371,7 @@
     </row>
     <row r="136" spans="1:15">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B136" s="2">
         <v>0.85416666666666663</v>
@@ -4397,7 +4394,7 @@
     </row>
     <row r="137" spans="1:15">
       <c r="A137" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B137" s="2">
         <v>0.89583333333333337</v>
@@ -4420,7 +4417,7 @@
     </row>
     <row r="138" spans="1:15">
       <c r="A138" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B138" s="2">
         <v>0.89583333333333337</v>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="139" spans="1:15">
       <c r="A139" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B139" s="2">
         <v>0.8125</v>
@@ -4466,7 +4463,7 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B140" s="2">
         <v>0.8125</v>
@@ -4489,7 +4486,7 @@
     </row>
     <row r="141" spans="1:15">
       <c r="A141" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B141" s="2">
         <v>0.85416666666666663</v>
@@ -4512,7 +4509,7 @@
     </row>
     <row r="142" spans="1:15">
       <c r="A142" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B142" s="2">
         <v>0.85416666666666663</v>
@@ -4535,7 +4532,7 @@
     </row>
     <row r="143" spans="1:15">
       <c r="A143" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B143" s="2">
         <v>0.89583333333333337</v>
@@ -4558,7 +4555,7 @@
     </row>
     <row r="144" spans="1:15">
       <c r="A144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B144" s="2">
         <v>0.89583333333333337</v>
@@ -4581,7 +4578,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B145" s="2">
         <v>0.89583333333333337</v>
@@ -4604,7 +4601,7 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B146" s="2">
         <v>0.8125</v>
@@ -4627,7 +4624,7 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B147" s="2">
         <v>0.8125</v>
@@ -4650,7 +4647,7 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B148" s="2">
         <v>0.85416666666666663</v>
@@ -4673,7 +4670,7 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B149" s="2">
         <v>0.85416666666666663</v>
@@ -4696,7 +4693,7 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B150" s="2">
         <v>0.89583333333333337</v>
@@ -4719,7 +4716,7 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B151" s="2">
         <v>0.89583333333333337</v>
@@ -4742,7 +4739,7 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B152" s="2">
         <v>0.8125</v>
@@ -4765,7 +4762,7 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B153" s="2">
         <v>0.8125</v>
@@ -4788,7 +4785,7 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B154" s="2">
         <v>0.85416666666666663</v>
@@ -4811,7 +4808,7 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B155" s="2">
         <v>0.85416666666666663</v>
@@ -4834,7 +4831,7 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B156" s="2">
         <v>0.89583333333333337</v>
@@ -4857,7 +4854,7 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B157" s="2">
         <v>0.89583333333333337</v>
@@ -4880,7 +4877,7 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B158" s="2">
         <v>0.8125</v>
@@ -4910,7 +4907,7 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B159" s="2">
         <v>0.8125</v>
@@ -4933,7 +4930,7 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B160" s="2">
         <v>0.85416666666666663</v>
@@ -4956,7 +4953,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B161" s="2">
         <v>0.85416666666666663</v>
@@ -4979,7 +4976,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B162" s="2">
         <v>0.89583333333333337</v>
@@ -5002,7 +4999,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B163" s="2">
         <v>0.89583333333333337</v>
@@ -5011,7 +5008,7 @@
         <v>12</v>
       </c>
       <c r="D163" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E163" t="s">
         <v>79</v>
@@ -5025,7 +5022,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B164" s="2">
         <v>0.8125</v>
@@ -5048,7 +5045,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B165" s="2">
         <v>0.85416666666666663</v>
@@ -5071,7 +5068,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B166" s="2">
         <v>0.89583333333333337</v>
@@ -5094,7 +5091,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B167" s="2">
         <v>0.8125</v>
@@ -5117,7 +5114,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B168" s="2">
         <v>0.85416666666666663</v>
@@ -5140,7 +5137,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B169" s="2">
         <v>0.89583333333333337</v>
@@ -5620,7 +5617,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2">
         <v>0.8125</v>
@@ -5635,7 +5632,7 @@
         <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G20" t="s">
         <v>144</v>
@@ -5643,7 +5640,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" s="2">
         <v>0.8125</v>
@@ -5666,7 +5663,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" s="2">
         <v>0.85416666666666663</v>
@@ -5681,7 +5678,7 @@
         <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G22" t="s">
         <v>144</v>
@@ -5689,7 +5686,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2">
         <v>0.85416666666666663</v>
@@ -5712,7 +5709,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B24" s="2">
         <v>0.89583333333333337</v>
@@ -5727,7 +5724,7 @@
         <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G24" t="s">
         <v>144</v>
@@ -5735,7 +5732,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B25" s="2">
         <v>0.89583333333333337</v>
@@ -5758,7 +5755,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
@@ -5773,7 +5770,7 @@
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G26" t="s">
         <v>144</v>
@@ -5781,7 +5778,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B27" s="2">
         <v>0.8125</v>
@@ -5804,7 +5801,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B28" s="2">
         <v>0.85416666666666663</v>
@@ -5819,7 +5816,7 @@
         <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
@@ -5827,7 +5824,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B29" s="2">
         <v>0.85416666666666663</v>
@@ -5850,7 +5847,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B30" s="2">
         <v>0.89583333333333337</v>
@@ -5865,7 +5862,7 @@
         <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G30" t="s">
         <v>144</v>
@@ -5873,7 +5870,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
@@ -5896,7 +5893,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
@@ -5919,7 +5916,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B33" s="2">
         <v>0.8125</v>
@@ -5934,7 +5931,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
@@ -5942,7 +5939,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B34" s="2">
         <v>0.85416666666666663</v>
@@ -5965,7 +5962,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B35" s="2">
         <v>0.85416666666666663</v>
@@ -5980,7 +5977,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G35" t="s">
         <v>144</v>
@@ -5988,7 +5985,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B36" s="2">
         <v>0.89583333333333337</v>
@@ -6011,7 +6008,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
@@ -6026,7 +6023,7 @@
         <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G37" t="s">
         <v>144</v>
@@ -6034,7 +6031,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -6057,7 +6054,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -6080,7 +6077,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -6627,7 +6624,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" s="2">
         <v>0.8125</v>
@@ -6642,7 +6639,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G23" t="s">
         <v>144</v>
@@ -6650,7 +6647,7 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" s="2">
         <v>0.85416666666666663</v>
@@ -6665,7 +6662,7 @@
         <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G24" t="s">
         <v>144</v>
@@ -6673,7 +6670,7 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B25" s="2">
         <v>0.89583333333333337</v>
@@ -6688,7 +6685,7 @@
         <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G25" t="s">
         <v>144</v>
@@ -6696,7 +6693,7 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
@@ -6711,7 +6708,7 @@
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G26" t="s">
         <v>144</v>
@@ -6719,7 +6716,7 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" s="2">
         <v>0.8125</v>
@@ -6734,7 +6731,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G27" t="s">
         <v>144</v>
@@ -6742,7 +6739,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B28" s="2">
         <v>0.85416666666666663</v>
@@ -6751,13 +6748,13 @@
         <v>188</v>
       </c>
       <c r="D28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E28" t="s">
         <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
@@ -6765,7 +6762,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B29" s="2">
         <v>0.85416666666666663</v>
@@ -6780,7 +6777,7 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G29" t="s">
         <v>144</v>
@@ -6788,7 +6785,7 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" s="2">
         <v>0.89583333333333337</v>
@@ -6803,7 +6800,7 @@
         <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G30" t="s">
         <v>144</v>
@@ -6811,7 +6808,7 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
@@ -6826,7 +6823,7 @@
         <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G31" t="s">
         <v>144</v>
@@ -6834,7 +6831,7 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
@@ -6849,7 +6846,7 @@
         <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G32" t="s">
         <v>144</v>
@@ -6864,13 +6861,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B33" s="2">
         <v>0.8125</v>
       </c>
       <c r="C33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D33" t="s">
         <v>186</v>
@@ -6879,7 +6876,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
@@ -6887,7 +6884,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B34" s="2">
         <v>0.85416666666666663</v>
@@ -6902,7 +6899,7 @@
         <v>78</v>
       </c>
       <c r="F34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G34" t="s">
         <v>144</v>
@@ -6910,7 +6907,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2">
         <v>0.85416666666666663</v>
@@ -6925,7 +6922,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G35" t="s">
         <v>144</v>
@@ -6933,7 +6930,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B36" s="2">
         <v>0.89583333333333337</v>
@@ -6948,7 +6945,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -6956,7 +6953,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B37" s="2">
         <v>0.89583333333333337</v>
@@ -6971,7 +6968,7 @@
         <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
         <v>144</v>
@@ -6979,7 +6976,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B38" s="2">
         <v>0.8125</v>
@@ -6994,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G38" t="s">
         <v>144</v>
@@ -7002,7 +6999,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -7017,7 +7014,7 @@
         <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G39" t="s">
         <v>144</v>
@@ -7025,7 +7022,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -7040,7 +7037,7 @@
         <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G40" t="s">
         <v>144</v>
@@ -7662,7 +7659,7 @@
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G26" t="s">
         <v>144</v>
@@ -7685,7 +7682,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G27" t="s">
         <v>144</v>
@@ -7708,7 +7705,7 @@
         <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
@@ -7722,7 +7719,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
@@ -7731,7 +7728,7 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G29" t="s">
         <v>144</v>
@@ -7754,7 +7751,7 @@
         <v>79</v>
       </c>
       <c r="F30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G30" t="s">
         <v>144</v>
@@ -7777,7 +7774,7 @@
         <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G31" t="s">
         <v>144</v>
@@ -7800,7 +7797,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G32" t="s">
         <v>144</v>
@@ -7830,7 +7827,7 @@
         <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
@@ -7844,7 +7841,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -7853,7 +7850,7 @@
         <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G34" t="s">
         <v>144</v>
@@ -7876,7 +7873,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G35" t="s">
         <v>144</v>
@@ -7884,7 +7881,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B36" s="2">
         <v>0.8125</v>
@@ -7899,7 +7896,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G36" t="s">
         <v>144</v>
@@ -7907,7 +7904,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2">
         <v>0.8125</v>
@@ -7922,7 +7919,7 @@
         <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G37" t="s">
         <v>144</v>
@@ -7930,7 +7927,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B38" s="2">
         <v>0.85416666666666663</v>
@@ -7945,7 +7942,7 @@
         <v>78</v>
       </c>
       <c r="F38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G38" t="s">
         <v>144</v>
@@ -7953,7 +7950,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B39" s="2">
         <v>0.85416666666666663</v>
@@ -7962,13 +7959,13 @@
         <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G39" t="s">
         <v>144</v>
@@ -7976,7 +7973,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B40" s="2">
         <v>0.89583333333333337</v>
@@ -7991,7 +7988,7 @@
         <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G40" t="s">
         <v>144</v>
@@ -7999,7 +7996,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B41" s="2">
         <v>0.89583333333333337</v>
@@ -8014,7 +8011,7 @@
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G41" t="s">
         <v>144</v>
@@ -8022,7 +8019,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B42" s="2">
         <v>0.8125</v>
@@ -8037,7 +8034,7 @@
         <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G42" t="s">
         <v>144</v>
@@ -8045,7 +8042,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B43" s="2">
         <v>0.85416666666666663</v>
@@ -8060,7 +8057,7 @@
         <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G43" t="s">
         <v>144</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6CBA20-2649-6D47-9092-D1D97CA381FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF600820-58A1-D24B-97E1-A868F99FC3BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="250">
   <si>
     <t>日期</t>
   </si>
@@ -839,6 +839,10 @@
   </si>
   <si>
     <t>豬臘 - QU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3807,7 +3811,7 @@
         <v>94</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>99</v>
+        <v>221</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6366,7 +6370,7 @@
         <v>202</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6389,7 +6393,7 @@
         <v>202</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6412,7 +6416,7 @@
         <v>202</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7432,7 +7436,7 @@
         <v>164</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -7455,7 +7459,7 @@
         <v>164</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>144</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:16">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF600820-58A1-D24B-97E1-A868F99FC3BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78625522-B01E-5441-BC7C-565291539FD3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -6439,7 +6439,7 @@
         <v>201</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6462,7 +6462,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6485,7 +6485,7 @@
         <v>201</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -6508,7 +6508,7 @@
         <v>200</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -6531,7 +6531,7 @@
         <v>201</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -6554,7 +6554,7 @@
         <v>200</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:17">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78625522-B01E-5441-BC7C-565291539FD3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF2F89-D60A-3B48-8127-43A00D612D81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="253">
   <si>
     <t>日期</t>
   </si>
@@ -844,6 +844,15 @@
   <si>
     <t>1-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/5 四</t>
+  </si>
+  <si>
+    <t>麵飽 - PAPAPA</t>
+  </si>
+  <si>
+    <t>8/5 五</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E0EA83-C783-7140-AD8B-B43A843048C1}">
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
@@ -4276,22 +4285,22 @@
     </row>
     <row r="132" spans="1:15">
       <c r="A132" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B132" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E132" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F132" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="G132" t="s">
         <v>144</v>
@@ -4299,22 +4308,22 @@
     </row>
     <row r="133" spans="1:15">
       <c r="A133" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B133" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C133" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="D133" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="E133" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F133" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G133" t="s">
         <v>144</v>
@@ -4322,40 +4331,33 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B134" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C134" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="D134" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="E134" t="s">
         <v>79</v>
       </c>
       <c r="F134" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G134" t="s">
         <v>144</v>
       </c>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
-      <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
     </row>
     <row r="135" spans="1:15">
       <c r="A135" t="s">
         <v>231</v>
       </c>
       <c r="B135" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C135" t="s">
         <v>80</v>
@@ -4378,7 +4380,7 @@
         <v>231</v>
       </c>
       <c r="B136" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C136" t="s">
         <v>80</v>
@@ -4395,13 +4397,20 @@
       <c r="G136" t="s">
         <v>144</v>
       </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1"/>
     </row>
     <row r="137" spans="1:15">
       <c r="A137" t="s">
         <v>231</v>
       </c>
       <c r="B137" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C137" t="s">
         <v>80</v>
@@ -4424,7 +4433,7 @@
         <v>231</v>
       </c>
       <c r="B138" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C138" t="s">
         <v>80</v>
@@ -4444,22 +4453,22 @@
     </row>
     <row r="139" spans="1:15">
       <c r="A139" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B139" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C139" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D139" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E139" t="s">
         <v>78</v>
       </c>
       <c r="F139" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s">
         <v>144</v>
@@ -4467,22 +4476,22 @@
     </row>
     <row r="140" spans="1:15">
       <c r="A140" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B140" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C140" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D140" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E140" t="s">
         <v>79</v>
       </c>
       <c r="F140" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G140" t="s">
         <v>144</v>
@@ -4493,19 +4502,19 @@
         <v>232</v>
       </c>
       <c r="B141" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C141" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="D141" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E141" t="s">
         <v>78</v>
       </c>
       <c r="F141" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G141" t="s">
         <v>144</v>
@@ -4516,19 +4525,19 @@
         <v>232</v>
       </c>
       <c r="B142" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C142" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D142" t="s">
-        <v>208</v>
+        <v>48</v>
       </c>
       <c r="E142" t="s">
         <v>79</v>
       </c>
       <c r="F142" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G142" t="s">
         <v>144</v>
@@ -4539,19 +4548,19 @@
         <v>232</v>
       </c>
       <c r="B143" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C143" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E143" t="s">
         <v>78</v>
       </c>
       <c r="F143" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G143" t="s">
         <v>144</v>
@@ -4562,19 +4571,19 @@
         <v>232</v>
       </c>
       <c r="B144" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C144" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D144" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="E144" t="s">
         <v>79</v>
       </c>
       <c r="F144" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G144" t="s">
         <v>144</v>
@@ -4582,22 +4591,22 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B145" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C145" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E145" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F145" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G145" t="s">
         <v>144</v>
@@ -4605,22 +4614,22 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B146" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C146" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D146" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F146" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G146" t="s">
         <v>144</v>
@@ -4628,22 +4637,22 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B147" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C147" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D147" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E147" t="s">
         <v>79</v>
       </c>
       <c r="F147" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G147" t="s">
         <v>144</v>
@@ -4654,7 +4663,7 @@
         <v>242</v>
       </c>
       <c r="B148" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C148" t="s">
         <v>80</v>
@@ -4677,7 +4686,7 @@
         <v>242</v>
       </c>
       <c r="B149" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C149" t="s">
         <v>80</v>
@@ -4700,7 +4709,7 @@
         <v>242</v>
       </c>
       <c r="B150" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C150" t="s">
         <v>80</v>
@@ -4723,7 +4732,7 @@
         <v>242</v>
       </c>
       <c r="B151" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C151" t="s">
         <v>80</v>
@@ -4743,22 +4752,22 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B152" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C152" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D152" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E152" t="s">
         <v>78</v>
       </c>
       <c r="F152" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G152" t="s">
         <v>144</v>
@@ -4766,22 +4775,22 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B153" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C153" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D153" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E153" t="s">
         <v>79</v>
       </c>
       <c r="F153" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G153" t="s">
         <v>144</v>
@@ -4792,19 +4801,19 @@
         <v>243</v>
       </c>
       <c r="B154" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C154" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D154" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E154" t="s">
         <v>78</v>
       </c>
       <c r="F154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G154" t="s">
         <v>144</v>
@@ -4815,19 +4824,19 @@
         <v>243</v>
       </c>
       <c r="B155" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C155" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D155" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E155" t="s">
         <v>79</v>
       </c>
       <c r="F155" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G155" t="s">
         <v>144</v>
@@ -4838,19 +4847,19 @@
         <v>243</v>
       </c>
       <c r="B156" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C156" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D156" t="s">
-        <v>203</v>
+        <v>67</v>
       </c>
       <c r="E156" t="s">
         <v>78</v>
       </c>
       <c r="F156" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G156" t="s">
         <v>144</v>
@@ -4861,19 +4870,19 @@
         <v>243</v>
       </c>
       <c r="B157" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C157" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D157" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E157" t="s">
         <v>79</v>
       </c>
       <c r="F157" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G157" t="s">
         <v>144</v>
@@ -4881,52 +4890,45 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B158" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C158" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D158" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="E158" t="s">
         <v>78</v>
       </c>
       <c r="F158" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G158" t="s">
         <v>144</v>
       </c>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
-      <c r="L158" s="1"/>
-      <c r="M158" s="1"/>
-      <c r="N158" s="1"/>
-      <c r="O158" s="1"/>
-      <c r="P158" s="1"/>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B159" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C159" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D159" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E159" t="s">
         <v>79</v>
       </c>
       <c r="F159" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G159" t="s">
         <v>144</v>
@@ -4937,42 +4939,49 @@
         <v>244</v>
       </c>
       <c r="B160" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C160" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D160" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="E160" t="s">
         <v>78</v>
       </c>
       <c r="F160" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G160" t="s">
         <v>144</v>
       </c>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
+      <c r="P160" s="1"/>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>244</v>
       </c>
       <c r="B161" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="D161" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="E161" t="s">
         <v>79</v>
       </c>
       <c r="F161" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G161" t="s">
         <v>144</v>
@@ -4983,13 +4992,13 @@
         <v>244</v>
       </c>
       <c r="B162" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C162" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E162" t="s">
         <v>78</v>
@@ -5006,19 +5015,19 @@
         <v>244</v>
       </c>
       <c r="B163" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C163" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
-        <v>248</v>
+        <v>6</v>
       </c>
       <c r="E163" t="s">
         <v>79</v>
       </c>
       <c r="F163" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G163" t="s">
         <v>144</v>
@@ -5026,22 +5035,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B164" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C164" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D164" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E164" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F164" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G164" t="s">
         <v>144</v>
@@ -5049,22 +5058,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B165" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C165" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D165" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="E165" t="s">
         <v>79</v>
       </c>
       <c r="F165" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G165" t="s">
         <v>144</v>
@@ -5075,19 +5084,19 @@
         <v>245</v>
       </c>
       <c r="B166" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C166" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E166" t="s">
         <v>79</v>
       </c>
       <c r="F166" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G166" t="s">
         <v>144</v>
@@ -5095,22 +5104,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B167" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C167" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E167" t="s">
         <v>79</v>
       </c>
       <c r="F167" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G167" t="s">
         <v>144</v>
@@ -5118,22 +5127,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B168" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E168" t="s">
         <v>79</v>
       </c>
       <c r="F168" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G168" t="s">
         <v>144</v>
@@ -5144,21 +5153,67 @@
         <v>247</v>
       </c>
       <c r="B169" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C169" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" t="s">
+        <v>24</v>
+      </c>
+      <c r="E169" t="s">
+        <v>79</v>
+      </c>
+      <c r="F169" t="s">
+        <v>83</v>
+      </c>
+      <c r="G169" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>247</v>
+      </c>
+      <c r="B170" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C170" t="s">
+        <v>21</v>
+      </c>
+      <c r="D170" t="s">
+        <v>23</v>
+      </c>
+      <c r="E170" t="s">
+        <v>79</v>
+      </c>
+      <c r="F170" t="s">
+        <v>83</v>
+      </c>
+      <c r="G170" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>247</v>
+      </c>
+      <c r="B171" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C171" t="s">
         <v>27</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D171" t="s">
         <v>29</v>
       </c>
-      <c r="E169" t="s">
-        <v>79</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="E171" t="s">
+        <v>79</v>
+      </c>
+      <c r="F171" t="s">
         <v>84</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G171" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5171,7 +5226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A652382C-1B8E-3D47-8B07-5935E173CD82}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5759,22 +5814,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="E26" t="s">
         <v>78</v>
       </c>
       <c r="F26" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="G26" t="s">
         <v>144</v>
@@ -5782,22 +5837,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B27" s="2">
         <v>0.8125</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="G27" t="s">
         <v>144</v>
@@ -5805,22 +5860,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E28" t="s">
         <v>78</v>
       </c>
       <c r="F28" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
@@ -5828,22 +5883,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B29" s="2">
         <v>0.85416666666666663</v>
       </c>
       <c r="C29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E29" t="s">
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="G29" t="s">
         <v>144</v>
@@ -5851,22 +5906,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B30" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="E30" t="s">
         <v>78</v>
       </c>
       <c r="F30" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="G30" t="s">
         <v>144</v>
@@ -5874,22 +5929,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B31" s="2">
         <v>0.89583333333333337</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E31" t="s">
         <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="G31" t="s">
         <v>144</v>
@@ -5897,16 +5952,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B32" s="2">
         <v>0.8125</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
         <v>78</v>
@@ -5920,22 +5975,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B33" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
@@ -5943,16 +5998,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
         <v>78</v>
@@ -5961,144 +6016,6 @@
         <v>198</v>
       </c>
       <c r="G34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>234</v>
-      </c>
-      <c r="B35" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C35" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" t="s">
-        <v>229</v>
-      </c>
-      <c r="G35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>234</v>
-      </c>
-      <c r="B36" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C36" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" t="s">
-        <v>171</v>
-      </c>
-      <c r="E36" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" t="s">
-        <v>198</v>
-      </c>
-      <c r="G36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>234</v>
-      </c>
-      <c r="B37" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C37" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" t="s">
-        <v>229</v>
-      </c>
-      <c r="G37" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>245</v>
-      </c>
-      <c r="B38" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C38" t="s">
-        <v>167</v>
-      </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F38" t="s">
-        <v>198</v>
-      </c>
-      <c r="G38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
-        <v>245</v>
-      </c>
-      <c r="B39" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C39" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" t="s">
-        <v>173</v>
-      </c>
-      <c r="E39" t="s">
-        <v>78</v>
-      </c>
-      <c r="F39" t="s">
-        <v>198</v>
-      </c>
-      <c r="G39" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
-        <v>245</v>
-      </c>
-      <c r="B40" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C40" t="s">
-        <v>178</v>
-      </c>
-      <c r="D40" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" t="s">
-        <v>198</v>
-      </c>
-      <c r="G40" t="s">
         <v>144</v>
       </c>
     </row>
@@ -6110,7 +6027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B38FBF-5FEC-5740-9062-B8355DB1F4DA}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -6488,7 +6405,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>193</v>
       </c>
@@ -6511,7 +6428,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -6534,7 +6451,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>193</v>
       </c>
@@ -6557,7 +6474,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>161</v>
       </c>
@@ -6580,7 +6497,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>161</v>
       </c>
@@ -6603,7 +6520,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>161</v>
       </c>
@@ -6626,424 +6543,562 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" t="s">
+        <v>240</v>
+      </c>
+      <c r="G24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>239</v>
+      </c>
+      <c r="G26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" t="s">
+        <v>239</v>
+      </c>
+      <c r="G27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
+        <v>239</v>
+      </c>
+      <c r="G28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
         <v>236</v>
       </c>
-      <c r="B23" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B29" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C29" t="s">
         <v>54</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D29" t="s">
         <v>191</v>
       </c>
-      <c r="E23" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" t="s">
         <v>239</v>
       </c>
-      <c r="G23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
+      <c r="G29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B30" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C30" t="s">
         <v>190</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D30" t="s">
         <v>171</v>
       </c>
-      <c r="E24" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" t="s">
         <v>239</v>
       </c>
-      <c r="G24" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" t="s">
+      <c r="G30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
         <v>236</v>
       </c>
-      <c r="B25" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B31" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C31" t="s">
         <v>157</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D31" t="s">
         <v>26</v>
       </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" t="s">
         <v>239</v>
       </c>
-      <c r="G25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" t="s">
+      <c r="G31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
         <v>237</v>
       </c>
-      <c r="B26" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B32" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C32" t="s">
         <v>187</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D32" t="s">
         <v>189</v>
       </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" t="s">
         <v>240</v>
       </c>
-      <c r="G26" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
+      <c r="G32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
         <v>237</v>
       </c>
-      <c r="B27" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B33" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C33" t="s">
         <v>167</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D33" t="s">
         <v>182</v>
       </c>
-      <c r="E27" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" t="s">
         <v>241</v>
       </c>
-      <c r="G27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" t="s">
+      <c r="G33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
         <v>237</v>
       </c>
-      <c r="B28" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B34" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C34" t="s">
         <v>188</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D34" t="s">
         <v>238</v>
       </c>
-      <c r="E28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" t="s">
         <v>240</v>
       </c>
-      <c r="G28" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29" t="s">
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
         <v>237</v>
       </c>
-      <c r="B29" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B35" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C35" t="s">
         <v>181</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D35" t="s">
         <v>184</v>
       </c>
-      <c r="E29" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E35" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" t="s">
         <v>241</v>
       </c>
-      <c r="G29" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30" t="s">
+      <c r="G35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
         <v>237</v>
       </c>
-      <c r="B30" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B36" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C36" t="s">
         <v>61</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D36" t="s">
         <v>186</v>
       </c>
-      <c r="E30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
         <v>240</v>
       </c>
-      <c r="G30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" t="s">
+      <c r="G36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
         <v>237</v>
       </c>
-      <c r="B31" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B37" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C37" t="s">
         <v>183</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D37" t="s">
         <v>180</v>
       </c>
-      <c r="E31" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" t="s">
         <v>241</v>
       </c>
-      <c r="G31" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" t="s">
+      <c r="G37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
         <v>246</v>
       </c>
-      <c r="B32" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B38" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C38" t="s">
         <v>184</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D38" t="s">
         <v>180</v>
       </c>
-      <c r="E32" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" t="s">
         <v>241</v>
       </c>
-      <c r="G32" t="s">
-        <v>144</v>
-      </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
         <v>246</v>
       </c>
-      <c r="B33" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B39" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C39" t="s">
         <v>238</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D39" t="s">
         <v>186</v>
       </c>
-      <c r="E33" t="s">
-        <v>79</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" t="s">
         <v>240</v>
       </c>
-      <c r="G33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+      <c r="G39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
         <v>246</v>
       </c>
-      <c r="B34" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B40" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C40" t="s">
         <v>167</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D40" t="s">
         <v>181</v>
       </c>
-      <c r="E34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" t="s">
         <v>241</v>
       </c>
-      <c r="G34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
+      <c r="G40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
         <v>246</v>
       </c>
-      <c r="B35" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B41" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C41" t="s">
         <v>187</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D41" t="s">
         <v>188</v>
       </c>
-      <c r="E35" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E41" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" t="s">
         <v>240</v>
       </c>
-      <c r="G35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
+      <c r="G41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
         <v>246</v>
       </c>
-      <c r="B36" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B42" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C42" t="s">
         <v>182</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D42" t="s">
         <v>183</v>
       </c>
-      <c r="E36" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" t="s">
         <v>241</v>
       </c>
-      <c r="G36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
+      <c r="G42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
         <v>246</v>
       </c>
-      <c r="B37" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B43" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C43" t="s">
         <v>189</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D43" t="s">
         <v>61</v>
       </c>
-      <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" t="s">
         <v>240</v>
       </c>
-      <c r="G37" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
+      <c r="G43" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
         <v>247</v>
       </c>
-      <c r="B38" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B44" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C44" t="s">
         <v>171</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D44" t="s">
         <v>26</v>
       </c>
-      <c r="E38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E44" t="s">
+        <v>78</v>
+      </c>
+      <c r="F44" t="s">
         <v>239</v>
       </c>
-      <c r="G38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
+      <c r="G44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
         <v>247</v>
       </c>
-      <c r="B39" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B45" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C45" t="s">
         <v>54</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D45" t="s">
         <v>190</v>
       </c>
-      <c r="E39" t="s">
-        <v>78</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E45" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" t="s">
         <v>239</v>
       </c>
-      <c r="G39" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
+      <c r="G45" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B46" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C46" t="s">
         <v>191</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D46" t="s">
         <v>157</v>
       </c>
-      <c r="E40" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E46" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" t="s">
         <v>239</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G46" t="s">
         <v>144</v>
       </c>
     </row>
@@ -7055,7 +7110,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F9B54F-1C5B-D04D-993A-929D11ED7A52}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -7691,6 +7746,13 @@
       <c r="G27" t="s">
         <v>144</v>
       </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
@@ -7763,22 +7825,22 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B31" s="2">
         <v>0.8125</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
         <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G31" t="s">
         <v>144</v>
@@ -7786,89 +7848,82 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B32" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F32" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G32" t="s">
         <v>144</v>
       </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B33" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
         <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G33" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B34" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" t="s">
+        <v>235</v>
+      </c>
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="C35" t="s">
         <v>28</v>
-      </c>
-      <c r="E34" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" t="s">
-        <v>227</v>
-      </c>
-      <c r="G34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>224</v>
-      </c>
-      <c r="B35" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="C35" t="s">
-        <v>145</v>
       </c>
       <c r="D35" t="s">
         <v>152</v>
@@ -7883,18 +7938,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>233</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s">
         <v>78</v>
@@ -7906,18 +7961,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>233</v>
       </c>
       <c r="B37" s="2">
-        <v>0.8125</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s">
         <v>79</v>
@@ -7929,18 +7984,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>233</v>
       </c>
       <c r="B38" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E38" t="s">
         <v>78</v>
@@ -7952,18 +8007,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>233</v>
       </c>
       <c r="B39" s="2">
-        <v>0.85416666666666663</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
@@ -7975,97 +8030,60 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B40" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G40" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B41" s="2">
-        <v>0.89583333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G41" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>236</v>
-      </c>
-      <c r="B42" s="2">
-        <v>0.8125</v>
-      </c>
-      <c r="C42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" t="s">
-        <v>226</v>
-      </c>
-      <c r="G42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>236</v>
-      </c>
-      <c r="B43" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="C43" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" t="s">
-        <v>157</v>
-      </c>
-      <c r="E43" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" t="s">
-        <v>226</v>
-      </c>
-      <c r="G43" t="s">
-        <v>144</v>
-      </c>
+    <row r="42" spans="1:16">
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FF2F89-D60A-3B48-8127-43A00D612D81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849B129-52F6-E248-A8AD-F9071918550B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="252">
   <si>
     <t>日期</t>
   </si>
@@ -847,9 +847,6 @@
   </si>
   <si>
     <t>7/5 四</t>
-  </si>
-  <si>
-    <t>麵飽 - PAPAPA</t>
   </si>
   <si>
     <t>8/5 五</t>
@@ -4285,7 +4282,7 @@
     </row>
     <row r="132" spans="1:15">
       <c r="A132" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B132" s="2">
         <v>0.8125</v>
@@ -4308,7 +4305,7 @@
     </row>
     <row r="133" spans="1:15">
       <c r="A133" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B133" s="2">
         <v>0.85416666666666663</v>
@@ -4331,7 +4328,7 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B134" s="2">
         <v>0.89583333333333337</v>
@@ -6600,7 +6597,7 @@
         <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E25" t="s">
         <v>79</v>
@@ -6614,7 +6611,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B26" s="2">
         <v>0.8125</v>
@@ -6637,7 +6634,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B27" s="2">
         <v>0.85416666666666663</v>
@@ -6660,7 +6657,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B28" s="2">
         <v>0.89583333333333337</v>

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849B129-52F6-E248-A8AD-F9071918550B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F1AA4C-2D74-CB4A-BB77-E4E870550B14}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -3978,7 +3978,7 @@
         <v>94</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4001,7 +4001,7 @@
         <v>97</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4024,7 +4024,7 @@
         <v>97</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4047,7 +4047,7 @@
         <v>97</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4070,7 +4070,7 @@
         <v>81</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4093,7 +4093,7 @@
         <v>81</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
     </row>
     <row r="124" spans="1:7">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F1AA4C-2D74-CB4A-BB77-E4E870550B14}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F6FFDC-F1E0-2646-B1C6-4D17B016CC48}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -7534,7 +7534,7 @@
         <v>162</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -7557,7 +7557,7 @@
         <v>163</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -7580,7 +7580,7 @@
         <v>162</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -7603,7 +7603,7 @@
         <v>163</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -7626,7 +7626,7 @@
         <v>162</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -7649,7 +7649,7 @@
         <v>163</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:16">

--- a/matches_data.xlsx
+++ b/matches_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/工人杯 2026 網頁素材/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F6FFDC-F1E0-2646-B1C6-4D17B016CC48}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E31066-0C50-294F-A7A1-023FD27E6824}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="3" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{0379C690-888D-FC44-B8DD-C33E1B7904AC}"/>
   </bookViews>
   <sheets>
     <sheet name="初級組_對賽安排" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="256">
   <si>
     <t>日期</t>
   </si>
@@ -850,6 +850,22 @@
   </si>
   <si>
     <t>8/5 五</t>
+  </si>
+  <si>
+    <t>8-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公務 - 勤蜂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1502,22 +1518,22 @@
         <v>110</v>
       </c>
       <c r="B11" s="2">
-        <v>0.8125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -4116,7 +4132,7 @@
         <v>82</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>99</v>
+        <v>221</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4139,7 +4155,7 @@
         <v>82</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>99</v>
+        <v>253</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4162,7 +4178,7 @@
         <v>83</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4176,7 +4192,7 @@
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="E127" t="s">
         <v>78</v>
@@ -4185,7 +4201,7 @@
         <v>83</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4208,7 +4224,7 @@
         <v>84</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -4231,7 +4247,7 @@
         <v>84</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130" spans="1:15">
@@ -4254,7 +4270,7 @@
         <v>85</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>99</v>
+        <v>254</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -5553,7 +5569,7 @@
         <v>197</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5576,7 +5592,7 @@
         <v>199</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5599,7 +5615,7 @@
         <v>197</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5622,7 +5638,7 @@
         <v>199</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5645,7 +5661,7 @@
         <v>197</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5668,7 +5684,7 @@
         <v>199</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6491,7 +6507,7 @@
         <v>200</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -6514,7 +6530,7 @@
         <v>200</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6537,7 +6553,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7672,7 +7688,7 @@
         <v>164</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -7695,7 +7711,7 @@
         <v>164</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:16">
